--- a/public/prices/price-current.xlsx
+++ b/public/prices/price-current.xlsx
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1130"/>
+  <dimension ref="A1:E1133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="11.25"/>
   <cols>
     <col width="2.6640625" customWidth="1" min="1" max="1"/>
@@ -12640,11 +12640,11 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>Blond Me Премиум-окислитель 12% 1000мл 2140321</t>
+          <t>Blond Me Обесцвечивающая пудра, premium lift 9+ 450г</t>
         </is>
       </c>
       <c r="C750" s="29" t="n">
-        <v>1209</v>
+        <v>2175.27</v>
       </c>
       <c r="D750" s="27" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>Blond Me Премиум-окислитель 2% 1000мл 2140315</t>
+          <t>Blond Me Премиум-окислитель 12% 1000мл 2140321</t>
         </is>
       </c>
       <c r="C751" s="29" t="n">
@@ -12669,14 +12669,14 @@
       </c>
       <c r="E751" s="28" t="n"/>
     </row>
-    <row r="752" ht="22.5" customHeight="1">
+    <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>NS Лосьон д/химической завивки нормальных волос №1 1000мл 1969343</t>
+          <t>Blond Me Премиум-окислитель 2% 1000мл 2140315</t>
         </is>
       </c>
       <c r="C752" s="29" t="n">
-        <v>1956.49</v>
+        <v>1209</v>
       </c>
       <c r="D752" s="27" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
     <row r="753" ht="22.5" customHeight="1">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>NS Лосьон д/химической завивки окрашенных волос №2 1000мл 1969347</t>
+          <t>NS Лосьон д/химической завивки для трудных волос №0 1000мл 1969344</t>
         </is>
       </c>
       <c r="C753" s="29" t="n">
@@ -12701,10 +12701,10 @@
       </c>
       <c r="E753" s="28" t="n"/>
     </row>
-    <row r="754">
+    <row r="754" ht="22.5" customHeight="1">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>NS Нейтрализатор для стойкого результата 1000мл 1969345</t>
+          <t>NS Лосьон д/химической завивки нормальных волос №1 1000мл 1969343</t>
         </is>
       </c>
       <c r="C754" s="29" t="n">
@@ -12717,46 +12717,46 @@
       </c>
       <c r="E754" s="28" t="n"/>
     </row>
-    <row r="755">
-      <c r="B755" s="7" t="inlineStr">
-        <is>
-          <t>Игора Варио Блонд PLUS (БЕЛАЯ БАНКА 7+) 450гр 2242113</t>
-        </is>
-      </c>
-      <c r="C755" s="10" t="n">
-        <v>1650</v>
-      </c>
-      <c r="D755" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E755" s="24" t="n"/>
-    </row>
-    <row r="756" ht="22.5" customHeight="1">
-      <c r="B756" s="7" t="inlineStr">
-        <is>
-          <t>Игора Варио Блонд SUPER PLUS (СИНЯЯ БАНКА 8+) 450 (НОВЫЙ ДИЗАЙН!) 2242115new</t>
-        </is>
-      </c>
-      <c r="C756" s="10" t="n">
-        <v>1650</v>
-      </c>
-      <c r="D756" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E756" s="24" t="n"/>
+    <row r="755" ht="22.5" customHeight="1">
+      <c r="B755" s="25" t="inlineStr">
+        <is>
+          <t>NS Лосьон д/химической завивки окрашенных волос №2 1000мл 1969347</t>
+        </is>
+      </c>
+      <c r="C755" s="29" t="n">
+        <v>1956.49</v>
+      </c>
+      <c r="D755" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E755" s="28" t="n"/>
+    </row>
+    <row r="756">
+      <c r="B756" s="25" t="inlineStr">
+        <is>
+          <t>NS Нейтрализатор для стойкого результата 1000мл 1969345</t>
+        </is>
+      </c>
+      <c r="C756" s="29" t="n">
+        <v>1956.49</v>
+      </c>
+      <c r="D756" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E756" s="28" t="n"/>
     </row>
     <row r="757">
       <c r="B757" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 0-00 Клир 60мл 60мл и000</t>
-        </is>
-      </c>
-      <c r="C757" s="8" t="n">
-        <v>455</v>
+          <t>Игора Варио Блонд PLUS (БЕЛАЯ БАНКА 7+) 450гр 2242113</t>
+        </is>
+      </c>
+      <c r="C757" s="10" t="n">
+        <v>1650</v>
       </c>
       <c r="D757" s="23" t="inlineStr">
         <is>
@@ -12765,14 +12765,14 @@
       </c>
       <c r="E757" s="24" t="n"/>
     </row>
-    <row r="758">
+    <row r="758" ht="22.5" customHeight="1">
       <c r="B758" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 0-33 Анти-красный микстон 60мл и033</t>
-        </is>
-      </c>
-      <c r="C758" s="8" t="n">
-        <v>455</v>
+          <t>Игора Варио Блонд SUPER PLUS (СИНЯЯ БАНКА 8+) 450 (НОВЫЙ ДИЗАЙН!) 2242115new</t>
+        </is>
+      </c>
+      <c r="C758" s="10" t="n">
+        <v>1650</v>
       </c>
       <c r="D758" s="23" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
     <row r="759">
       <c r="B759" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 0-77 Медный микстон 60мл и077</t>
+          <t>Краска IR 0-00 Клир 60мл 60мл и000</t>
         </is>
       </c>
       <c r="C759" s="8" t="n">
@@ -12800,7 +12800,7 @@
     <row r="760">
       <c r="B760" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 0-89 Красно-фиолетовый микстон 60мл и089</t>
+          <t>Краска IR 0-33 Анти-красный микстон 60мл и033</t>
         </is>
       </c>
       <c r="C760" s="8" t="n">
@@ -12816,7 +12816,7 @@
     <row r="761">
       <c r="B761" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 0-99 Фиолетовый микстон 60мл и099</t>
+          <t>Краска IR 0-77 Медный микстон 60мл и077</t>
         </is>
       </c>
       <c r="C761" s="8" t="n">
@@ -12832,7 +12832,7 @@
     <row r="762">
       <c r="B762" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 1-0 Черный натуральный 60мл и1</t>
+          <t>Краска IR 0-89 Красно-фиолетовый микстон 60мл и089</t>
         </is>
       </c>
       <c r="C762" s="8" t="n">
@@ -12848,7 +12848,7 @@
     <row r="763">
       <c r="B763" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 1-1 Черный сандрэ 60мл и11</t>
+          <t>Краска IR 0-99 Фиолетовый микстон 60мл и099</t>
         </is>
       </c>
       <c r="C763" s="8" t="n">
@@ -12864,7 +12864,7 @@
     <row r="764">
       <c r="B764" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 3-0 Темный коричневый натуральный 60мл и30</t>
+          <t>Краска IR 1-0 Черный натуральный 60мл и1</t>
         </is>
       </c>
       <c r="C764" s="8" t="n">
@@ -12877,10 +12877,10 @@
       </c>
       <c r="E764" s="24" t="n"/>
     </row>
-    <row r="765" ht="22.5" customHeight="1">
+    <row r="765">
       <c r="B765" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 3-65 Темный коричневый шоколадный золотистый 60мл и365</t>
+          <t>Краска IR 1-1 Черный сандрэ 60мл и11</t>
         </is>
       </c>
       <c r="C765" s="8" t="n">
@@ -12896,7 +12896,7 @@
     <row r="766">
       <c r="B766" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 3-68 Темный коричневый шоколадный красный 60мл и368</t>
+          <t>Краска IR 3-0 Темный коричневый натуральный 60мл и30</t>
         </is>
       </c>
       <c r="C766" s="8" t="n">
@@ -12909,10 +12909,10 @@
       </c>
       <c r="E766" s="24" t="n"/>
     </row>
-    <row r="767">
+    <row r="767" ht="22.5" customHeight="1">
       <c r="B767" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 4-0 Средний коричневый натуральный 60мл и40</t>
+          <t>Краска IR 3-65 Темный коричневый шоколадный золотистый 60мл и365</t>
         </is>
       </c>
       <c r="C767" s="8" t="n">
@@ -12928,7 +12928,7 @@
     <row r="768">
       <c r="B768" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 4-6 Средний коричневый шоколадный 60мл и46</t>
+          <t>Краска IR 3-68 Темный коричневый шоколадный красный 60мл и368</t>
         </is>
       </c>
       <c r="C768" s="8" t="n">
@@ -12941,10 +12941,10 @@
       </c>
       <c r="E768" s="24" t="n"/>
     </row>
-    <row r="769" ht="22.5" customHeight="1">
+    <row r="769">
       <c r="B769" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 4-63 Средний коричневый шоколадный матовый 60мл и463</t>
+          <t>Краска IR 4-0 Средний коричневый натуральный 60мл и40</t>
         </is>
       </c>
       <c r="C769" s="8" t="n">
@@ -12960,7 +12960,7 @@
     <row r="770">
       <c r="B770" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 4-68 Средний коричневый шокол.красный 60мл и468</t>
+          <t>Краска IR 4-6 Средний коричневый шоколадный 60мл и46</t>
         </is>
       </c>
       <c r="C770" s="8" t="n">
@@ -12973,10 +12973,10 @@
       </c>
       <c r="E770" s="24" t="n"/>
     </row>
-    <row r="771">
+    <row r="771" ht="22.5" customHeight="1">
       <c r="B771" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 4-88 Средний коричневый красный экстра 60мл и488</t>
+          <t>Краска IR 4-63 Средний коричневый шоколадный матовый 60мл и463</t>
         </is>
       </c>
       <c r="C771" s="8" t="n">
@@ -12992,7 +12992,7 @@
     <row r="772">
       <c r="B772" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 5-0 Светлый коричневый натуральный 60мл и50</t>
+          <t>Краска IR 4-68 Средний коричневый шокол.красный 60мл и468</t>
         </is>
       </c>
       <c r="C772" s="8" t="n">
@@ -13008,7 +13008,7 @@
     <row r="773">
       <c r="B773" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 5-00 Светлый коричневый натуральный экстра 60мл и500</t>
+          <t>Краска IR 4-88 Средний коричневый красный экстра 60мл и488</t>
         </is>
       </c>
       <c r="C773" s="8" t="n">
@@ -13024,7 +13024,7 @@
     <row r="774">
       <c r="B774" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 5-1 Светлый коричневый сандрэ 60мл и51</t>
+          <t>Краска IR 5-0 Светлый коричневый натуральный 60мл и50</t>
         </is>
       </c>
       <c r="C774" s="8" t="n">
@@ -13040,7 +13040,7 @@
     <row r="775">
       <c r="B775" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 5-16 Светлый коричневый сандрэ шоколадный 60мл и516</t>
+          <t>Краска IR 5-00 Светлый коричневый натуральный экстра 60мл и500</t>
         </is>
       </c>
       <c r="C775" s="8" t="n">
@@ -13056,7 +13056,7 @@
     <row r="776">
       <c r="B776" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 5-4 Светлый коричневый бежевый 60мл и54</t>
+          <t>Краска IR 5-1 Светлый коричневый сандрэ 60мл и51</t>
         </is>
       </c>
       <c r="C776" s="8" t="n">
@@ -13072,7 +13072,7 @@
     <row r="777">
       <c r="B777" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 5-6 Светлый коричневы й шоколадный 60мл и56</t>
+          <t>Краска IR 5-16 Светлый коричневый сандрэ шоколадный 60мл и516</t>
         </is>
       </c>
       <c r="C777" s="8" t="n">
@@ -13085,10 +13085,10 @@
       </c>
       <c r="E777" s="24" t="n"/>
     </row>
-    <row r="778" ht="22.5" customHeight="1">
+    <row r="778">
       <c r="B778" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 5-65 Светлый коричневы шоколадный золотистый 60мл и565</t>
+          <t>Краска IR 5-4 Светлый коричневый бежевый 60мл и54</t>
         </is>
       </c>
       <c r="C778" s="8" t="n">
@@ -13104,7 +13104,7 @@
     <row r="779">
       <c r="B779" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 5-7 Светлый коричневый медный 60мл и57</t>
+          <t>Краска IR 5-6 Светлый коричневы й шоколадный 60мл и56</t>
         </is>
       </c>
       <c r="C779" s="8" t="n">
@@ -13117,10 +13117,10 @@
       </c>
       <c r="E779" s="24" t="n"/>
     </row>
-    <row r="780">
+    <row r="780" ht="22.5" customHeight="1">
       <c r="B780" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 5-88 Светлый коричневый красный экстра 60мл и588</t>
+          <t>Краска IR 5-65 Светлый коричневы шоколадный золотистый 60мл и565</t>
         </is>
       </c>
       <c r="C780" s="8" t="n">
@@ -13136,7 +13136,7 @@
     <row r="781">
       <c r="B781" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 6-0 Темный русый натуральный 60мл и60</t>
+          <t>Краска IR 5-7 Светлый коричневый медный 60мл и57</t>
         </is>
       </c>
       <c r="C781" s="8" t="n">
@@ -13152,7 +13152,7 @@
     <row r="782">
       <c r="B782" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 6-00 Темный русый натуральный экстра 60мл и600</t>
+          <t>Краска IR 5-88 Светлый коричневый красный экстра 60мл и588</t>
         </is>
       </c>
       <c r="C782" s="8" t="n">
@@ -13168,7 +13168,7 @@
     <row r="783">
       <c r="B783" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 6-12 Темный русый сандрэ пепельный  60мл и612</t>
+          <t>Краска IR 6-0 Темный русый натуральный 60мл и60</t>
         </is>
       </c>
       <c r="C783" s="8" t="n">
@@ -13184,7 +13184,7 @@
     <row r="784">
       <c r="B784" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 6-16 Темный русый сандрэ шоколадный   60мл и616</t>
+          <t>Краска IR 6-00 Темный русый натуральный экстра 60мл и600</t>
         </is>
       </c>
       <c r="C784" s="8" t="n">
@@ -13200,7 +13200,7 @@
     <row r="785">
       <c r="B785" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 6-29 Темный русый пепельный фиолетовый 60мл и629</t>
+          <t>Краска IR 6-12 Темный русый сандрэ пепельный  60мл и612</t>
         </is>
       </c>
       <c r="C785" s="8" t="n">
@@ -13216,7 +13216,7 @@
     <row r="786">
       <c r="B786" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 6-4 Темный русый бежевый 60мл и64</t>
+          <t>Краска IR 6-16 Темный русый сандрэ шоколадный   60мл и616</t>
         </is>
       </c>
       <c r="C786" s="8" t="n">
@@ -13232,7 +13232,7 @@
     <row r="787">
       <c r="B787" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 6-46 Темный русый бежевый шоколадный 60мл и646</t>
+          <t>Краска IR 6-29 Темный русый пепельный фиолетовый 60мл и629</t>
         </is>
       </c>
       <c r="C787" s="8" t="n">
@@ -13248,7 +13248,7 @@
     <row r="788">
       <c r="B788" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 6-6 Темный русый шоколадный   60мл и66</t>
+          <t>Краска IR 6-4 Темный русый бежевый 60мл и64</t>
         </is>
       </c>
       <c r="C788" s="8" t="n">
@@ -13264,7 +13264,7 @@
     <row r="789">
       <c r="B789" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 6-65 Темный русый шоколадный золотистый 60мл и665</t>
+          <t>Краска IR 6-46 Темный русый бежевый шоколадный 60мл и646</t>
         </is>
       </c>
       <c r="C789" s="8" t="n">
@@ -13280,7 +13280,7 @@
     <row r="790">
       <c r="B790" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 6-68 Темный русый шоколадный красный 60мл и668</t>
+          <t>Краска IR 6-6 Темный русый шоколадный   60мл и66</t>
         </is>
       </c>
       <c r="C790" s="8" t="n">
@@ -13296,7 +13296,7 @@
     <row r="791">
       <c r="B791" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 6-77 Темный русый медный экстра 60мл и677</t>
+          <t>Краска IR 6-65 Темный русый шоколадный золотистый 60мл и665</t>
         </is>
       </c>
       <c r="C791" s="8" t="n">
@@ -13312,7 +13312,7 @@
     <row r="792">
       <c r="B792" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 6-88 Темный русый красный экстра 60мл и688</t>
+          <t>Краска IR 6-68 Темный русый шоколадный красный 60мл и668</t>
         </is>
       </c>
       <c r="C792" s="8" t="n">
@@ -13328,7 +13328,7 @@
     <row r="793">
       <c r="B793" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 6-99 Темный русый фиолетовый экстра 60мл и699</t>
+          <t>Краска IR 6-77 Темный русый медный экстра 60мл и677</t>
         </is>
       </c>
       <c r="C793" s="8" t="n">
@@ -13344,7 +13344,7 @@
     <row r="794">
       <c r="B794" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 7-0 Средний русый натуральный 60мл и70</t>
+          <t>Краска IR 6-88 Темный русый красный экстра 60мл и688</t>
         </is>
       </c>
       <c r="C794" s="8" t="n">
@@ -13360,7 +13360,7 @@
     <row r="795">
       <c r="B795" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 7-4 Средний русый бежевый 60мл и74</t>
+          <t>Краска IR 6-99 Темный русый фиолетовый экстра 60мл и699</t>
         </is>
       </c>
       <c r="C795" s="8" t="n">
@@ -13376,7 +13376,7 @@
     <row r="796">
       <c r="B796" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 7-42 Средний русый бежевый пепельный 60мл и742</t>
+          <t>Краска IR 7-0 Средний русый натуральный 60мл и70</t>
         </is>
       </c>
       <c r="C796" s="8" t="n">
@@ -13392,7 +13392,7 @@
     <row r="797">
       <c r="B797" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 7-55 Средний русый золотистый экстра 60мл и755</t>
+          <t>Краска IR 7-4 Средний русый бежевый 60мл и74</t>
         </is>
       </c>
       <c r="C797" s="8" t="n">
@@ -13408,7 +13408,7 @@
     <row r="798">
       <c r="B798" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 7-77 Средний русый медный экстра 60мл и777</t>
+          <t>Краска IR 7-42 Средний русый бежевый пепельный 60мл и742</t>
         </is>
       </c>
       <c r="C798" s="8" t="n">
@@ -13424,7 +13424,7 @@
     <row r="799">
       <c r="B799" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 8-0 Светлый русый натуральный 60мл и80</t>
+          <t>Краска IR 7-55 Средний русый золотистый экстра 60мл и755</t>
         </is>
       </c>
       <c r="C799" s="8" t="n">
@@ -13440,7 +13440,7 @@
     <row r="800">
       <c r="B800" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 8-00 Светлый русый натуральный экстра 60мл и800</t>
+          <t>Краска IR 7-77 Средний русый медный экстра 60мл и777</t>
         </is>
       </c>
       <c r="C800" s="8" t="n">
@@ -13456,7 +13456,7 @@
     <row r="801">
       <c r="B801" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 8-1 Светлый русый сандрэ 60мл и81</t>
+          <t>Краска IR 8-0 Светлый русый натуральный 60мл и80</t>
         </is>
       </c>
       <c r="C801" s="8" t="n">
@@ -13472,7 +13472,7 @@
     <row r="802">
       <c r="B802" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 8-11 Светлый русый сандрэ экстра 60мл и811</t>
+          <t>Краска IR 8-00 Светлый русый натуральный экстра 60мл и800</t>
         </is>
       </c>
       <c r="C802" s="8" t="n">
@@ -13488,7 +13488,7 @@
     <row r="803">
       <c r="B803" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 8-19 Светлый русый сандрэ фиолетовый 60мл и819</t>
+          <t>Краска IR 8-1 Светлый русый сандрэ 60мл и81</t>
         </is>
       </c>
       <c r="C803" s="8" t="n">
@@ -13504,7 +13504,7 @@
     <row r="804">
       <c r="B804" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 8-21 Светлый русый пепельный сандрэ 60мл и821</t>
+          <t>Краска IR 8-11 Светлый русый сандрэ экстра 60мл и811</t>
         </is>
       </c>
       <c r="C804" s="8" t="n">
@@ -13520,7 +13520,7 @@
     <row r="805">
       <c r="B805" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 8-4 Светлый русый бежевый 60мл и84</t>
+          <t>Краска IR 8-19 Светлый русый сандрэ фиолетовый 60мл и819</t>
         </is>
       </c>
       <c r="C805" s="8" t="n">
@@ -13536,7 +13536,7 @@
     <row r="806">
       <c r="B806" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 9-0 Блондин натуральный 60мл и90</t>
+          <t>Краска IR 8-21 Светлый русый пепельный сандрэ 60мл и821</t>
         </is>
       </c>
       <c r="C806" s="8" t="n">
@@ -13552,7 +13552,7 @@
     <row r="807">
       <c r="B807" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 9-00 Блондин натуральный экстра 60мл и900</t>
+          <t>Краска IR 8-4 Светлый русый бежевый 60мл и84</t>
         </is>
       </c>
       <c r="C807" s="8" t="n">
@@ -13568,7 +13568,7 @@
     <row r="808">
       <c r="B808" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 9-4 Блондин бежевый 60мл и94</t>
+          <t>Краска IR 9-0 Блондин натуральный 60мл и90</t>
         </is>
       </c>
       <c r="C808" s="8" t="n">
@@ -13584,7 +13584,7 @@
     <row r="809">
       <c r="B809" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 9-55 Блондин золотистый экстра 60мл и955</t>
+          <t>Краска IR 9-00 Блондин натуральный экстра 60мл и900</t>
         </is>
       </c>
       <c r="C809" s="8" t="n">
@@ -13600,7 +13600,7 @@
     <row r="810">
       <c r="B810" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 9-7 Блондин медный 60мл и97</t>
+          <t>Краска IR 9-4 Блондин бежевый 60мл и94</t>
         </is>
       </c>
       <c r="C810" s="8" t="n">
@@ -13616,7 +13616,7 @@
     <row r="811">
       <c r="B811" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 9-98 Блондин фиолетовый красный 60мл и998</t>
+          <t>Краска IR 9-55 Блондин золотистый экстра 60мл и955</t>
         </is>
       </c>
       <c r="C811" s="8" t="n">
@@ -13632,7 +13632,7 @@
     <row r="812">
       <c r="B812" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 9,5-1 Светлый блондин пастельный сандрэ 60мл и951</t>
+          <t>Краска IR 9-7 Блондин медный 60мл и97</t>
         </is>
       </c>
       <c r="C812" s="8" t="n">
@@ -13648,7 +13648,7 @@
     <row r="813">
       <c r="B813" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 9,5-4 Светлый блондин пастельный сандрэ 60мл и954</t>
+          <t>Краска IR 9-98 Блондин фиолетовый красный 60мл и998</t>
         </is>
       </c>
       <c r="C813" s="8" t="n">
@@ -13661,10 +13661,10 @@
       </c>
       <c r="E813" s="24" t="n"/>
     </row>
-    <row r="814" ht="22.5" customHeight="1">
+    <row r="814">
       <c r="B814" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 9,5-49 Светлый блондин пастельный перламутровый 60мл и9549</t>
+          <t>Краска IR 9,5-1 Светлый блондин пастельный сандрэ 60мл и951</t>
         </is>
       </c>
       <c r="C814" s="8" t="n">
@@ -13677,14 +13677,14 @@
       </c>
       <c r="E814" s="24" t="n"/>
     </row>
-    <row r="815" ht="22.5" customHeight="1">
+    <row r="815">
       <c r="B815" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 4-60 Средний коричневый шоколадный натурал. 60мл и460</t>
+          <t>Краска IR 9,5-4 Светлый блондин пастельный сандрэ 60мл и954</t>
         </is>
       </c>
       <c r="C815" s="8" t="n">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="D815" s="23" t="inlineStr">
         <is>
@@ -13696,11 +13696,11 @@
     <row r="816" ht="22.5" customHeight="1">
       <c r="B816" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 5-50 Светлый коричн.золотистый натуральный 60мл и550</t>
+          <t>Краска IR 9,5-49 Светлый блондин пастельный перламутровый 60мл и9549</t>
         </is>
       </c>
       <c r="C816" s="8" t="n">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="D816" s="23" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
     <row r="817" ht="22.5" customHeight="1">
       <c r="B817" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 5-60 Светлый коричн.шоколадный натуральный 60мл и560</t>
+          <t>Краска IR AB 4-60 Средний коричневый шоколадный натурал. 60мл и460</t>
         </is>
       </c>
       <c r="C817" s="8" t="n">
@@ -13725,10 +13725,10 @@
       </c>
       <c r="E817" s="24" t="n"/>
     </row>
-    <row r="818">
+    <row r="818" ht="22.5" customHeight="1">
       <c r="B818" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 5-80 Светлый коричн.красный натуральный 60мл и580</t>
+          <t>Краска IR AB 5-50 Светлый коричн.золотистый натуральный 60мл и550</t>
         </is>
       </c>
       <c r="C818" s="8" t="n">
@@ -13744,7 +13744,7 @@
     <row r="819" ht="22.5" customHeight="1">
       <c r="B819" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 6-50 Темный русый золотистый натуральный 60мл и650</t>
+          <t>Краска IR AB 5-60 Светлый коричн.шоколадный натуральный 60мл и560</t>
         </is>
       </c>
       <c r="C819" s="8" t="n">
@@ -13757,10 +13757,10 @@
       </c>
       <c r="E819" s="24" t="n"/>
     </row>
-    <row r="820" ht="22.5" customHeight="1">
+    <row r="820">
       <c r="B820" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 6-60 Темный русый шоколадный натуральный 60мл и660</t>
+          <t>Краска IR AB 5-80 Светлый коричн.красный натуральный 60мл и580</t>
         </is>
       </c>
       <c r="C820" s="8" t="n">
@@ -13773,10 +13773,10 @@
       </c>
       <c r="E820" s="24" t="n"/>
     </row>
-    <row r="821">
+    <row r="821" ht="22.5" customHeight="1">
       <c r="B821" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 6-70 Темный русый медный натуральный 60мл и670</t>
+          <t>Краска IR AB 6-50 Темный русый золотистый натуральный 60мл и650</t>
         </is>
       </c>
       <c r="C821" s="8" t="n">
@@ -13789,10 +13789,10 @@
       </c>
       <c r="E821" s="24" t="n"/>
     </row>
-    <row r="822">
+    <row r="822" ht="22.5" customHeight="1">
       <c r="B822" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 6-80 Темный русый красный натуральный 60мл и680</t>
+          <t>Краска IR AB 6-60 Темный русый шоколадный натуральный 60мл и660</t>
         </is>
       </c>
       <c r="C822" s="8" t="n">
@@ -13808,7 +13808,7 @@
     <row r="823">
       <c r="B823" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 7-10 Средний русый натуральный сандрэ 60мл и710</t>
+          <t>Краска IR AB 6-70 Темный русый медный натуральный 60мл и670</t>
         </is>
       </c>
       <c r="C823" s="8" t="n">
@@ -13821,10 +13821,10 @@
       </c>
       <c r="E823" s="24" t="n"/>
     </row>
-    <row r="824" ht="22.5" customHeight="1">
+    <row r="824">
       <c r="B824" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 7-50 Средний русый золотистый натуральный 60мл и750</t>
+          <t>Краска IR AB 6-80 Темный русый красный натуральный 60мл и680</t>
         </is>
       </c>
       <c r="C824" s="8" t="n">
@@ -13840,7 +13840,7 @@
     <row r="825">
       <c r="B825" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 7-70 Средний русый медный натуральный 60мл и770</t>
+          <t>Краска IR AB 7-10 Средний русый натуральный сандрэ 60мл и710</t>
         </is>
       </c>
       <c r="C825" s="8" t="n">
@@ -13853,10 +13853,10 @@
       </c>
       <c r="E825" s="24" t="n"/>
     </row>
-    <row r="826">
+    <row r="826" ht="22.5" customHeight="1">
       <c r="B826" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 8-01 60мл и801</t>
+          <t>Краска IR AB 7-50 Средний русый золотистый натуральный 60мл и750</t>
         </is>
       </c>
       <c r="C826" s="8" t="n">
@@ -13869,10 +13869,10 @@
       </c>
       <c r="E826" s="24" t="n"/>
     </row>
-    <row r="827" ht="22.5" customHeight="1">
+    <row r="827">
       <c r="B827" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 8-50  Светлый русый золотистый натуральный 60мл и850</t>
+          <t>Краска IR AB 7-70 Средний русый медный натуральный 60мл и770</t>
         </is>
       </c>
       <c r="C827" s="8" t="n">
@@ -13885,10 +13885,10 @@
       </c>
       <c r="E827" s="24" t="n"/>
     </row>
-    <row r="828" ht="22.5" customHeight="1">
+    <row r="828">
       <c r="B828" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 8-60 Светлый русый шоколадный натуральный 60мл и860</t>
+          <t>Краска IR AB 8-01 60мл и801</t>
         </is>
       </c>
       <c r="C828" s="8" t="n">
@@ -13901,10 +13901,10 @@
       </c>
       <c r="E828" s="24" t="n"/>
     </row>
-    <row r="829">
+    <row r="829" ht="22.5" customHeight="1">
       <c r="B829" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 9-40 Блондин бежевый натуральный 60мл и940</t>
+          <t>Краска IR AB 8-50  Светлый русый золотистый натуральный 60мл и850</t>
         </is>
       </c>
       <c r="C829" s="8" t="n">
@@ -13917,10 +13917,10 @@
       </c>
       <c r="E829" s="24" t="n"/>
     </row>
-    <row r="830">
+    <row r="830" ht="22.5" customHeight="1">
       <c r="B830" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 9-50 Блондин золотистый натуральный 60мл и950</t>
+          <t>Краска IR AB 8-60 Светлый русый шоколадный натуральный 60мл и860</t>
         </is>
       </c>
       <c r="C830" s="8" t="n">
@@ -13936,7 +13936,7 @@
     <row r="831">
       <c r="B831" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 9-60 Блондин шоколадный натуральный 60мл и960</t>
+          <t>Краска IR AB 9-40 Блондин бежевый натуральный 60мл и940</t>
         </is>
       </c>
       <c r="C831" s="8" t="n">
@@ -13952,7 +13952,7 @@
     <row r="832">
       <c r="B832" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 10-0 Экстрасветлый блондин натуральный 60мл и100</t>
+          <t>Краска IR AB 9-50 Блондин золотистый натуральный 60мл и950</t>
         </is>
       </c>
       <c r="C832" s="8" t="n">
@@ -13968,7 +13968,7 @@
     <row r="833">
       <c r="B833" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 10-1 Экстрасветлый блондин сандрэ 60мл и101</t>
+          <t>Краска IR AB 9-60 Блондин шоколадный натуральный 60мл и960</t>
         </is>
       </c>
       <c r="C833" s="8" t="n">
@@ -13981,10 +13981,10 @@
       </c>
       <c r="E833" s="24" t="n"/>
     </row>
-    <row r="834" ht="22.5" customHeight="1">
+    <row r="834">
       <c r="B834" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 10-19 Экстрасветлый блондин сандрэ фиолетовый 60мл и1019</t>
+          <t>Краска IR HL 10-0 Экстрасветлый блондин натуральный 60мл и100</t>
         </is>
       </c>
       <c r="C834" s="8" t="n">
@@ -13997,10 +13997,10 @@
       </c>
       <c r="E834" s="24" t="n"/>
     </row>
-    <row r="835" ht="22.5" customHeight="1">
+    <row r="835">
       <c r="B835" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 10-21 Экстрасветлый блондин пепельн. сандрэ 60мл и1021</t>
+          <t>Краска IR HL 10-1 Экстрасветлый блондин сандрэ 60мл и101</t>
         </is>
       </c>
       <c r="C835" s="8" t="n">
@@ -14013,10 +14013,10 @@
       </c>
       <c r="E835" s="24" t="n"/>
     </row>
-    <row r="836">
+    <row r="836" ht="22.5" customHeight="1">
       <c r="B836" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 10-4 Экстрасветлый блондин бежевый 60мл и104</t>
+          <t>Краска IR HL 10-19 Экстрасветлый блондин сандрэ фиолетовый 60мл и1019</t>
         </is>
       </c>
       <c r="C836" s="8" t="n">
@@ -14029,10 +14029,10 @@
       </c>
       <c r="E836" s="24" t="n"/>
     </row>
-    <row r="837">
+    <row r="837" ht="22.5" customHeight="1">
       <c r="B837" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 12-0 Спец. блондин натуральный 60мл и120</t>
+          <t>Краска IR HL 10-21 Экстрасветлый блондин пепельн. сандрэ 60мл и1021</t>
         </is>
       </c>
       <c r="C837" s="8" t="n">
@@ -14048,7 +14048,7 @@
     <row r="838">
       <c r="B838" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 12-19 Спец. блондин фиолетовый сандрэ 60мл и1219</t>
+          <t>Краска IR HL 10-4 Экстрасветлый блондин бежевый 60мл и104</t>
         </is>
       </c>
       <c r="C838" s="8" t="n">
@@ -14064,7 +14064,7 @@
     <row r="839">
       <c r="B839" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 12-2 Спец. блондин пепельный 60мл и122</t>
+          <t>Краска IR HL 12-0 Спец. блондин натуральный 60мл и120</t>
         </is>
       </c>
       <c r="C839" s="8" t="n">
@@ -14080,7 +14080,7 @@
     <row r="840">
       <c r="B840" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 12-21 Спец. блондин пепельный сандрэ 60мл и1221</t>
+          <t>Краска IR HL 12-19 Спец. блондин фиолетовый сандрэ 60мл и1219</t>
         </is>
       </c>
       <c r="C840" s="8" t="n">
@@ -14094,41 +14094,41 @@
       <c r="E840" s="24" t="n"/>
     </row>
     <row r="841">
-      <c r="B841" s="25" t="inlineStr">
-        <is>
-          <t>Оксигент на масляной основе 12% 1000 мл 2184627</t>
-        </is>
-      </c>
-      <c r="C841" s="26" t="n">
-        <v>929.0700000000001</v>
-      </c>
-      <c r="D841" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E841" s="28" t="n"/>
+      <c r="B841" s="7" t="inlineStr">
+        <is>
+          <t>Краска IR HL 12-2 Спец. блондин пепельный 60мл и122</t>
+        </is>
+      </c>
+      <c r="C841" s="8" t="n">
+        <v>475</v>
+      </c>
+      <c r="D841" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E841" s="24" t="n"/>
     </row>
     <row r="842">
-      <c r="B842" s="25" t="inlineStr">
-        <is>
-          <t>Оксигент на масляной основе 3% 1000 мл 2184625</t>
-        </is>
-      </c>
-      <c r="C842" s="26" t="n">
-        <v>929.0700000000001</v>
-      </c>
-      <c r="D842" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E842" s="28" t="n"/>
+      <c r="B842" s="7" t="inlineStr">
+        <is>
+          <t>Краска IR HL 12-21 Спец. блондин пепельный сандрэ 60мл и1221</t>
+        </is>
+      </c>
+      <c r="C842" s="8" t="n">
+        <v>475</v>
+      </c>
+      <c r="D842" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E842" s="24" t="n"/>
     </row>
     <row r="843">
       <c r="B843" s="25" t="inlineStr">
         <is>
-          <t>Оксигент на масляной основе 6% 1000 мл 2184628</t>
+          <t>Оксигент на масляной основе 12% 1000 мл 2184627</t>
         </is>
       </c>
       <c r="C843" s="26" t="n">
@@ -14141,24 +14141,30 @@
       </c>
       <c r="E843" s="28" t="n"/>
     </row>
-    <row r="844" ht="14.25" customHeight="1">
-      <c r="B844" s="12" t="inlineStr">
-        <is>
-          <t>OSIS - Укладка</t>
-        </is>
-      </c>
-      <c r="C844" s="17" t="n"/>
-      <c r="D844" s="22" t="n"/>
-      <c r="E844" s="22" t="n"/>
+    <row r="844">
+      <c r="B844" s="25" t="inlineStr">
+        <is>
+          <t>Оксигент на масляной основе 3% 1000 мл 2184625</t>
+        </is>
+      </c>
+      <c r="C844" s="26" t="n">
+        <v>929.0700000000001</v>
+      </c>
+      <c r="D844" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E844" s="28" t="n"/>
     </row>
     <row r="845">
       <c r="B845" s="25" t="inlineStr">
         <is>
-          <t>Лак д/волос №2 фикс. 3+ СФ FREEZE 300 мл. 1970454</t>
+          <t>Оксигент на масляной основе 6% 1000 мл 2184628</t>
         </is>
       </c>
       <c r="C845" s="26" t="n">
-        <v>750.97</v>
+        <v>929.0700000000001</v>
       </c>
       <c r="D845" s="27" t="inlineStr">
         <is>
@@ -14170,85 +14176,85 @@
     <row r="846">
       <c r="B846" s="25" t="inlineStr">
         <is>
+          <t>Оксигент на масляной основе 9% 1000 мл 1847105</t>
+        </is>
+      </c>
+      <c r="C846" s="26" t="n">
+        <v>929.0700000000001</v>
+      </c>
+      <c r="D846" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E846" s="28" t="n"/>
+    </row>
+    <row r="847" ht="14.25" customHeight="1">
+      <c r="B847" s="12" t="inlineStr">
+        <is>
+          <t>OSIS - Укладка</t>
+        </is>
+      </c>
+      <c r="C847" s="17" t="n"/>
+      <c r="D847" s="22" t="n"/>
+      <c r="E847" s="22" t="n"/>
+    </row>
+    <row r="848">
+      <c r="B848" s="25" t="inlineStr">
+        <is>
+          <t>Лак д/волос №2 фикс. 3+ СФ FREEZE 300 мл. 1970454</t>
+        </is>
+      </c>
+      <c r="C848" s="26" t="n">
+        <v>750.97</v>
+      </c>
+      <c r="D848" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E848" s="28" t="n"/>
+    </row>
+    <row r="849">
+      <c r="B849" s="25" t="inlineStr">
+        <is>
           <t>Лак д/волос №2 фикс. 3+ СФ FREEZE 500 мл. 1970621</t>
         </is>
       </c>
-      <c r="C846" s="26" t="n">
+      <c r="C849" s="26" t="n">
         <v>909.0700000000001</v>
       </c>
-      <c r="D846" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E846" s="28" t="n"/>
-    </row>
-    <row r="847">
-      <c r="B847" s="7" t="inlineStr">
+      <c r="D849" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E849" s="28" t="n"/>
+    </row>
+    <row r="850">
+      <c r="B850" s="7" t="inlineStr">
         <is>
           <t>Лак д/волос №3 фикс. 4+ ЭСФ SESSION 300 мл. 1970645</t>
         </is>
       </c>
-      <c r="C847" s="8" t="n">
+      <c r="C850" s="8" t="n">
         <v>807.5</v>
       </c>
-      <c r="D847" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E847" s="24" t="n"/>
-    </row>
-    <row r="848">
-      <c r="B848" s="7" t="inlineStr">
-        <is>
-          <t>Спрей с бриллиантовым блеском Sparkler 300 мл. 1970641</t>
-        </is>
-      </c>
-      <c r="C848" s="8" t="n">
-        <v>988.55</v>
-      </c>
-      <c r="D848" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E848" s="24" t="n"/>
-    </row>
-    <row r="849">
-      <c r="B849" s="7" t="inlineStr">
-        <is>
-          <t>Спрей термозащитный Super Shield 300мл 4045787936612</t>
-        </is>
-      </c>
-      <c r="C849" s="8" t="n">
-        <v>708.05</v>
-      </c>
-      <c r="D849" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E849" s="24" t="n"/>
-    </row>
-    <row r="850" ht="14.25" customHeight="1">
-      <c r="B850" s="12" t="inlineStr">
-        <is>
-          <t>SILHOUETTE/Professionnelle - Укладка</t>
-        </is>
-      </c>
-      <c r="C850" s="17" t="n"/>
-      <c r="D850" s="22" t="n"/>
-      <c r="E850" s="22" t="n"/>
+      <c r="D850" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E850" s="24" t="n"/>
     </row>
     <row r="851">
       <c r="B851" s="7" t="inlineStr">
         <is>
-          <t>Professionnelle Лак СФ  (Венгрия) 500 мл. 8701</t>
+          <t>Спрей с бриллиантовым блеском Sparkler 300 мл. 1970641</t>
         </is>
       </c>
       <c r="C851" s="8" t="n">
-        <v>830</v>
+        <v>988.55</v>
       </c>
       <c r="D851" s="23" t="inlineStr">
         <is>
@@ -14260,11 +14266,11 @@
     <row r="852">
       <c r="B852" s="7" t="inlineStr">
         <is>
-          <t>Безупречный спрей ультрасильной фиксации 200 мл 2646468</t>
+          <t>Спрей термозащитный Super Shield 300мл 4045787936612</t>
         </is>
       </c>
       <c r="C852" s="8" t="n">
-        <v>767</v>
+        <v>708.05</v>
       </c>
       <c r="D852" s="23" t="inlineStr">
         <is>
@@ -14273,114 +14279,108 @@
       </c>
       <c r="E852" s="24" t="n"/>
     </row>
-    <row r="853">
-      <c r="B853" s="7" t="inlineStr">
-        <is>
-          <t>Гель д/волос сверхсильной фиксации 250мл 2147236</t>
-        </is>
-      </c>
-      <c r="C853" s="8" t="n">
-        <v>660</v>
-      </c>
-      <c r="D853" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E853" s="24" t="n"/>
+    <row r="853" ht="14.25" customHeight="1">
+      <c r="B853" s="12" t="inlineStr">
+        <is>
+          <t>SILHOUETTE/Professionnelle - Укладка</t>
+        </is>
+      </c>
+      <c r="C853" s="17" t="n"/>
+      <c r="D853" s="22" t="n"/>
+      <c r="E853" s="22" t="n"/>
     </row>
     <row r="854">
       <c r="B854" s="7" t="inlineStr">
         <is>
+          <t>Professionnelle Лак СФ  (Венгрия) 500 мл. 8701</t>
+        </is>
+      </c>
+      <c r="C854" s="8" t="n">
+        <v>830</v>
+      </c>
+      <c r="D854" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E854" s="24" t="n"/>
+    </row>
+    <row r="855">
+      <c r="B855" s="7" t="inlineStr">
+        <is>
+          <t>Безупречный спрей ультрасильной фиксации 200 мл 2646468</t>
+        </is>
+      </c>
+      <c r="C855" s="8" t="n">
+        <v>767</v>
+      </c>
+      <c r="D855" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E855" s="24" t="n"/>
+    </row>
+    <row r="856">
+      <c r="B856" s="7" t="inlineStr">
+        <is>
+          <t>Гель д/волос сверхсильной фиксации 250мл 2147236</t>
+        </is>
+      </c>
+      <c r="C856" s="8" t="n">
+        <v>660</v>
+      </c>
+      <c r="D856" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E856" s="24" t="n"/>
+    </row>
+    <row r="857">
+      <c r="B857" s="7" t="inlineStr">
+        <is>
           <t>Лак для волос ультрасильной фиксации 500мл 1937472/1581304</t>
         </is>
       </c>
-      <c r="C854" s="8" t="n">
+      <c r="C857" s="8" t="n">
         <v>820</v>
       </c>
-      <c r="D854" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E854" s="24" t="n"/>
-    </row>
-    <row r="855" ht="15" customHeight="1">
-      <c r="B855" s="5" t="inlineStr">
+      <c r="D857" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E857" s="24" t="n"/>
+    </row>
+    <row r="858" ht="15" customHeight="1">
+      <c r="B858" s="5" t="inlineStr">
         <is>
           <t>WELLA</t>
         </is>
       </c>
-      <c r="C855" s="16" t="n"/>
-      <c r="D855" s="22" t="n"/>
-      <c r="E855" s="22" t="n"/>
-    </row>
-    <row r="856" ht="14.25" customHeight="1">
-      <c r="B856" s="12" t="inlineStr">
+      <c r="C858" s="16" t="n"/>
+      <c r="D858" s="22" t="n"/>
+      <c r="E858" s="22" t="n"/>
+    </row>
+    <row r="859" ht="14.25" customHeight="1">
+      <c r="B859" s="12" t="inlineStr">
         <is>
           <t>EIMI - Укладка</t>
         </is>
       </c>
-      <c r="C856" s="17" t="n"/>
-      <c r="D856" s="22" t="n"/>
-      <c r="E856" s="22" t="n"/>
-    </row>
-    <row r="857">
-      <c r="B857" s="25" t="inlineStr">
-        <is>
-          <t>лак перфоманс ЭСФ 500 мл 11198/4138</t>
-        </is>
-      </c>
-      <c r="C857" s="29" t="n">
-        <v>939.11</v>
-      </c>
-      <c r="D857" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E857" s="28" t="n"/>
-    </row>
-    <row r="858">
-      <c r="B858" s="25" t="inlineStr">
-        <is>
-          <t>Пена EIMI д/укладки №2 НФ 300 мл NATURAL VOLUME 11199/1642</t>
-        </is>
-      </c>
-      <c r="C858" s="26" t="n">
-        <v>915.4</v>
-      </c>
-      <c r="D858" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E858" s="28" t="n"/>
-    </row>
-    <row r="859">
-      <c r="B859" s="25" t="inlineStr">
-        <is>
-          <t>Пена EIMI д/укладки №2 НФ 500мл NATURAL VOLUME 11020/9594</t>
-        </is>
-      </c>
-      <c r="C859" s="29" t="n">
-        <v>1292.94</v>
-      </c>
-      <c r="D859" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E859" s="28" t="n"/>
+      <c r="C859" s="17" t="n"/>
+      <c r="D859" s="22" t="n"/>
+      <c r="E859" s="22" t="n"/>
     </row>
     <row r="860">
       <c r="B860" s="25" t="inlineStr">
         <is>
-          <t>Спрей EIMI д/объема Body Crafter 150мл. 43744/1743</t>
-        </is>
-      </c>
-      <c r="C860" s="26" t="n">
-        <v>915.4</v>
+          <t>лак перфоманс ЭСФ 500 мл 11198/4138</t>
+        </is>
+      </c>
+      <c r="C860" s="29" t="n">
+        <v>939.11</v>
       </c>
       <c r="D860" s="27" t="inlineStr">
         <is>
@@ -14389,10 +14389,10 @@
       </c>
       <c r="E860" s="28" t="n"/>
     </row>
-    <row r="861" ht="22.5" customHeight="1">
+    <row r="861">
       <c r="B861" s="25" t="inlineStr">
         <is>
-          <t>Спрей EIMI д/обьема текстуры, сахарный Sugar Lift 150мл 43750/6050</t>
+          <t>Пена EIMI д/укладки №2 НФ 300 мл NATURAL VOLUME 11199/1642</t>
         </is>
       </c>
       <c r="C861" s="26" t="n">
@@ -14408,11 +14408,11 @@
     <row r="862">
       <c r="B862" s="25" t="inlineStr">
         <is>
-          <t>Спрей EIMI минеральный текстур. Ocean Spritz 150мл. 43747/1687</t>
-        </is>
-      </c>
-      <c r="C862" s="26" t="n">
-        <v>915.4</v>
+          <t>Пена EIMI д/укладки №2 НФ 500мл NATURAL VOLUME 11020/9594</t>
+        </is>
+      </c>
+      <c r="C862" s="29" t="n">
+        <v>1292.94</v>
       </c>
       <c r="D862" s="27" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
     <row r="863">
       <c r="B863" s="25" t="inlineStr">
         <is>
-          <t>Спрей EIMI термозащитный №2 THERMAL IMAGЕ 150мл 43742/1691</t>
+          <t>Спрей EIMI д/объема Body Crafter 150мл. 43744/1743</t>
         </is>
       </c>
       <c r="C863" s="26" t="n">
@@ -14437,84 +14437,84 @@
       </c>
       <c r="E863" s="28" t="n"/>
     </row>
-    <row r="864">
+    <row r="864" ht="22.5" customHeight="1">
       <c r="B864" s="25" t="inlineStr">
         <is>
+          <t>Спрей EIMI д/обьема текстуры, сахарный Sugar Lift 150мл 43750/6050</t>
+        </is>
+      </c>
+      <c r="C864" s="26" t="n">
+        <v>915.4</v>
+      </c>
+      <c r="D864" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E864" s="28" t="n"/>
+    </row>
+    <row r="865">
+      <c r="B865" s="25" t="inlineStr">
+        <is>
+          <t>Спрей EIMI минеральный текстур. Ocean Spritz 150мл. 43747/1687</t>
+        </is>
+      </c>
+      <c r="C865" s="26" t="n">
+        <v>915.4</v>
+      </c>
+      <c r="D865" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E865" s="28" t="n"/>
+    </row>
+    <row r="866">
+      <c r="B866" s="25" t="inlineStr">
+        <is>
+          <t>Спрей EIMI термозащитный №2 THERMAL IMAGЕ 150мл 43742/1691</t>
+        </is>
+      </c>
+      <c r="C866" s="26" t="n">
+        <v>915.4</v>
+      </c>
+      <c r="D866" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E866" s="28" t="n"/>
+    </row>
+    <row r="867">
+      <c r="B867" s="25" t="inlineStr">
+        <is>
           <t>Спрей-мусс EIMI д.прик.объема Root Shoot  200мл 43130/9213</t>
         </is>
       </c>
-      <c r="C864" s="26" t="n">
+      <c r="C867" s="26" t="n">
         <v>918.24</v>
       </c>
-      <c r="D864" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E864" s="28" t="n"/>
-    </row>
-    <row r="865" ht="14.25" customHeight="1">
-      <c r="B865" s="12" t="inlineStr">
+      <c r="D867" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E867" s="28" t="n"/>
+    </row>
+    <row r="868" ht="14.25" customHeight="1">
+      <c r="B868" s="12" t="inlineStr">
         <is>
           <t>Illumina - Красители</t>
         </is>
       </c>
-      <c r="C865" s="17" t="n"/>
-      <c r="D865" s="22" t="n"/>
-      <c r="E865" s="22" t="n"/>
-    </row>
-    <row r="866">
-      <c r="B866" s="7" t="inlineStr">
-        <is>
-          <t>Illumina color Лиловое Серебро 71371</t>
-        </is>
-      </c>
-      <c r="C866" s="8" t="n">
-        <v>759</v>
-      </c>
-      <c r="D866" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E866" s="24" t="n"/>
-    </row>
-    <row r="867">
-      <c r="B867" s="7" t="inlineStr">
-        <is>
-          <t>Illumina color Платиновая лилия 71418</t>
-        </is>
-      </c>
-      <c r="C867" s="8" t="n">
-        <v>759</v>
-      </c>
-      <c r="D867" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E867" s="24" t="n"/>
-    </row>
-    <row r="868">
-      <c r="B868" s="25" t="inlineStr">
-        <is>
-          <t>Illumina color Титановый Розовый 08971</t>
-        </is>
-      </c>
-      <c r="C868" s="26" t="n">
-        <v>705.87</v>
-      </c>
-      <c r="D868" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E868" s="28" t="n"/>
+      <c r="C868" s="17" t="n"/>
+      <c r="D868" s="22" t="n"/>
+      <c r="E868" s="22" t="n"/>
     </row>
     <row r="869">
       <c r="B869" s="7" t="inlineStr">
         <is>
-          <t>Краска 10/ Яркий блонд 60мл 10/</t>
+          <t>Illumina color Лиловое Серебро 71371</t>
         </is>
       </c>
       <c r="C869" s="8" t="n">
@@ -14530,7 +14530,7 @@
     <row r="870">
       <c r="B870" s="7" t="inlineStr">
         <is>
-          <t>Краска 10/05 Яркий блонд натуральный махагоновый 60мл 10/05</t>
+          <t>Illumina color Платиновая лилия 71418</t>
         </is>
       </c>
       <c r="C870" s="8" t="n">
@@ -14544,25 +14544,25 @@
       <c r="E870" s="24" t="n"/>
     </row>
     <row r="871">
-      <c r="B871" s="7" t="inlineStr">
-        <is>
-          <t>Краска 10/1 Яркий блонд пепельный 60мл 10/1</t>
-        </is>
-      </c>
-      <c r="C871" s="8" t="n">
-        <v>759</v>
-      </c>
-      <c r="D871" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E871" s="24" t="n"/>
+      <c r="B871" s="25" t="inlineStr">
+        <is>
+          <t>Illumina color Титановый Розовый 08971</t>
+        </is>
+      </c>
+      <c r="C871" s="26" t="n">
+        <v>705.87</v>
+      </c>
+      <c r="D871" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E871" s="28" t="n"/>
     </row>
     <row r="872">
       <c r="B872" s="7" t="inlineStr">
         <is>
-          <t>Краска 10/34 Яркий блонд золотистый красный 60мл 10/34</t>
+          <t>Краска 10/ Яркий блонд 60мл 10/</t>
         </is>
       </c>
       <c r="C872" s="8" t="n">
@@ -14578,7 +14578,7 @@
     <row r="873">
       <c r="B873" s="7" t="inlineStr">
         <is>
-          <t>Краска 10/36 Яркий блонд золотисто-фиолетовый 60мл 10/36</t>
+          <t>Краска 10/05 Яркий блонд натуральный махагоновый 60мл 10/05</t>
         </is>
       </c>
       <c r="C873" s="8" t="n">
@@ -14594,7 +14594,7 @@
     <row r="874">
       <c r="B874" s="7" t="inlineStr">
         <is>
-          <t>Краска 10/38 Яркий блонд золотисто-жемчужный 60мл 10/38</t>
+          <t>Краска 10/1 Яркий блонд пепельный 60мл 10/1</t>
         </is>
       </c>
       <c r="C874" s="8" t="n">
@@ -14610,7 +14610,7 @@
     <row r="875">
       <c r="B875" s="7" t="inlineStr">
         <is>
-          <t>Краска 10/69 Яркий блонд фиолетовый сандрэ 60мл 10/69</t>
+          <t>Краска 10/34 Яркий блонд золотистый красный 60мл 10/34</t>
         </is>
       </c>
       <c r="C875" s="8" t="n">
@@ -14626,7 +14626,7 @@
     <row r="876">
       <c r="B876" s="7" t="inlineStr">
         <is>
-          <t>Краска 10/81 Яркий блондин жемчужно-пепельный 60мл 10/81</t>
+          <t>Краска 10/36 Яркий блонд золотисто-фиолетовый 60мл 10/36</t>
         </is>
       </c>
       <c r="C876" s="8" t="n">
@@ -14642,7 +14642,7 @@
     <row r="877">
       <c r="B877" s="7" t="inlineStr">
         <is>
-          <t>Краска 10/93 Яркий блонд золотистый сандрэ 60мл 10/93</t>
+          <t>Краска 10/38 Яркий блонд золотисто-жемчужный 60мл 10/38</t>
         </is>
       </c>
       <c r="C877" s="8" t="n">
@@ -14658,7 +14658,7 @@
     <row r="878">
       <c r="B878" s="7" t="inlineStr">
         <is>
-          <t>Краска 4/ Коричневый 60мл 4/</t>
+          <t>Краска 10/69 Яркий блонд фиолетовый сандрэ 60мл 10/69</t>
         </is>
       </c>
       <c r="C878" s="8" t="n">
@@ -14674,7 +14674,7 @@
     <row r="879">
       <c r="B879" s="7" t="inlineStr">
         <is>
-          <t>Краска 5/ Светло-коричневый 60мл 5/</t>
+          <t>Краска 10/81 Яркий блондин жемчужно-пепельный 60мл 10/81</t>
         </is>
       </c>
       <c r="C879" s="8" t="n">
@@ -14688,25 +14688,25 @@
       <c r="E879" s="24" t="n"/>
     </row>
     <row r="880">
-      <c r="B880" s="25" t="inlineStr">
-        <is>
-          <t>Краска 5/02 Светло-коричневый натуральный матовый 60мл 5/02</t>
-        </is>
-      </c>
-      <c r="C880" s="26" t="n">
-        <v>705.87</v>
-      </c>
-      <c r="D880" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E880" s="28" t="n"/>
+      <c r="B880" s="7" t="inlineStr">
+        <is>
+          <t>Краска 10/93 Яркий блонд золотистый сандрэ 60мл 10/93</t>
+        </is>
+      </c>
+      <c r="C880" s="8" t="n">
+        <v>759</v>
+      </c>
+      <c r="D880" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E880" s="24" t="n"/>
     </row>
     <row r="881">
       <c r="B881" s="7" t="inlineStr">
         <is>
-          <t>Краска 5/35 Светло-коричневый золотисто-махагоновый 60мл 5/35</t>
+          <t>Краска 4/ Коричневый 60мл 4/</t>
         </is>
       </c>
       <c r="C881" s="8" t="n">
@@ -14722,7 +14722,7 @@
     <row r="882">
       <c r="B882" s="7" t="inlineStr">
         <is>
-          <t>Краска 5/7 Светло-коричневый коричневый 60мл 5/7</t>
+          <t>Краска 5/ Светло-коричневый 60мл 5/</t>
         </is>
       </c>
       <c r="C882" s="8" t="n">
@@ -14736,25 +14736,25 @@
       <c r="E882" s="24" t="n"/>
     </row>
     <row r="883">
-      <c r="B883" s="7" t="inlineStr">
-        <is>
-          <t>Краска 5/81 Светло-коричневый жемчужно-пепельный 60мл 5/81</t>
-        </is>
-      </c>
-      <c r="C883" s="8" t="n">
-        <v>759</v>
-      </c>
-      <c r="D883" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E883" s="24" t="n"/>
+      <c r="B883" s="25" t="inlineStr">
+        <is>
+          <t>Краска 5/02 Светло-коричневый натуральный матовый 60мл 5/02</t>
+        </is>
+      </c>
+      <c r="C883" s="26" t="n">
+        <v>705.87</v>
+      </c>
+      <c r="D883" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E883" s="28" t="n"/>
     </row>
     <row r="884">
       <c r="B884" s="7" t="inlineStr">
         <is>
-          <t>Краска 6/ Темный блонд 60мл 6/</t>
+          <t>Краска 5/35 Светло-коричневый золотисто-махагоновый 60мл 5/35</t>
         </is>
       </c>
       <c r="C884" s="8" t="n">
@@ -14770,7 +14770,7 @@
     <row r="885">
       <c r="B885" s="7" t="inlineStr">
         <is>
-          <t>Краска 6/16 Темный блонд пепельный фиолетовый 60мл 6/16</t>
+          <t>Краска 5/7 Светло-коричневый коричневый 60мл 5/7</t>
         </is>
       </c>
       <c r="C885" s="8" t="n">
@@ -14786,7 +14786,7 @@
     <row r="886">
       <c r="B886" s="7" t="inlineStr">
         <is>
-          <t>Краска 6/19 Темный блонд пепельный сандрэ 60мл 6/19</t>
+          <t>Краска 5/81 Светло-коричневый жемчужно-пепельный 60мл 5/81</t>
         </is>
       </c>
       <c r="C886" s="8" t="n">
@@ -14802,7 +14802,7 @@
     <row r="887">
       <c r="B887" s="7" t="inlineStr">
         <is>
-          <t>Краска 6/76 Темный блонд коричнево-фиолетовый 60мл 6/76</t>
+          <t>Краска 6/ Темный блонд 60мл 6/</t>
         </is>
       </c>
       <c r="C887" s="8" t="n">
@@ -14818,7 +14818,7 @@
     <row r="888">
       <c r="B888" s="7" t="inlineStr">
         <is>
-          <t>Краска 7/ Блонд 60мл 7/</t>
+          <t>Краска 6/16 Темный блонд пепельный фиолетовый 60мл 6/16</t>
         </is>
       </c>
       <c r="C888" s="8" t="n">
@@ -14834,7 +14834,7 @@
     <row r="889">
       <c r="B889" s="7" t="inlineStr">
         <is>
-          <t>Краска 7/31 Блонд золотисто-пепельный 60мл 7/31</t>
+          <t>Краска 6/19 Темный блонд пепельный сандрэ 60мл 6/19</t>
         </is>
       </c>
       <c r="C889" s="8" t="n">
@@ -14850,7 +14850,7 @@
     <row r="890">
       <c r="B890" s="7" t="inlineStr">
         <is>
-          <t>Краска 7/42 Блонд красно-золотистый матовый 60мл NEW 7/42</t>
+          <t>Краска 6/76 Темный блонд коричнево-фиолетовый 60мл 6/76</t>
         </is>
       </c>
       <c r="C890" s="8" t="n">
@@ -14866,7 +14866,7 @@
     <row r="891">
       <c r="B891" s="7" t="inlineStr">
         <is>
-          <t>Краска 7/7 Блонд коричневый 60мл 7/7</t>
+          <t>Краска 7/ Блонд 60мл 7/</t>
         </is>
       </c>
       <c r="C891" s="8" t="n">
@@ -14882,7 +14882,7 @@
     <row r="892">
       <c r="B892" s="7" t="inlineStr">
         <is>
-          <t>Краска 8/ Светлый блонд 60мл 8/</t>
+          <t>Краска 7/31 Блонд золотисто-пепельный 60мл 7/31</t>
         </is>
       </c>
       <c r="C892" s="8" t="n">
@@ -14898,7 +14898,7 @@
     <row r="893">
       <c r="B893" s="7" t="inlineStr">
         <is>
-          <t>Краска 8/36 Светлый блонд золотисто-фиолетовый 60мл NEW 8/36</t>
+          <t>Краска 7/42 Блонд красно-золотистый матовый 60мл NEW 7/42</t>
         </is>
       </c>
       <c r="C893" s="8" t="n">
@@ -14914,7 +14914,7 @@
     <row r="894">
       <c r="B894" s="7" t="inlineStr">
         <is>
-          <t>Краска 8/38 Светлый блонд золотисто-жемчужный 60мл 8/38</t>
+          <t>Краска 7/7 Блонд коричневый 60мл 7/7</t>
         </is>
       </c>
       <c r="C894" s="8" t="n">
@@ -14930,7 +14930,7 @@
     <row r="895">
       <c r="B895" s="7" t="inlineStr">
         <is>
-          <t>Краска 8/69 Светлый блонд фиолетовый сандрэ 60мл 8/69</t>
+          <t>Краска 8/ Светлый блонд 60мл 8/</t>
         </is>
       </c>
       <c r="C895" s="8" t="n">
@@ -14946,7 +14946,7 @@
     <row r="896">
       <c r="B896" s="7" t="inlineStr">
         <is>
-          <t>Краска 8/93 Светлый блондин сандрэ золотистый 60мл 8/93</t>
+          <t>Краска 8/36 Светлый блонд золотисто-фиолетовый 60мл NEW 8/36</t>
         </is>
       </c>
       <c r="C896" s="8" t="n">
@@ -14962,7 +14962,7 @@
     <row r="897">
       <c r="B897" s="7" t="inlineStr">
         <is>
-          <t>Краска 9/ Очень светлый блонд 60мл 9/</t>
+          <t>Краска 8/38 Светлый блонд золотисто-жемчужный 60мл 8/38</t>
         </is>
       </c>
       <c r="C897" s="8" t="n">
@@ -14975,10 +14975,10 @@
       </c>
       <c r="E897" s="24" t="n"/>
     </row>
-    <row r="898" ht="22.5" customHeight="1">
+    <row r="898">
       <c r="B898" s="7" t="inlineStr">
         <is>
-          <t>Краска 9/03 Очень светлый блонд натуральный золотистый 60мл 9/03</t>
+          <t>Краска 8/69 Светлый блонд фиолетовый сандрэ 60мл 8/69</t>
         </is>
       </c>
       <c r="C898" s="8" t="n">
@@ -14994,7 +14994,7 @@
     <row r="899">
       <c r="B899" s="7" t="inlineStr">
         <is>
-          <t>Краска 9/19 Очень светлый блонд пепельный сандрэ 60мл 9/19</t>
+          <t>Краска 8/93 Светлый блондин сандрэ золотистый 60мл 8/93</t>
         </is>
       </c>
       <c r="C899" s="8" t="n">
@@ -15007,10 +15007,10 @@
       </c>
       <c r="E899" s="24" t="n"/>
     </row>
-    <row r="900" ht="22.5" customHeight="1">
+    <row r="900">
       <c r="B900" s="7" t="inlineStr">
         <is>
-          <t>Краска 9/37 Очень светлый блонд золотисто-коричневый 60мл NEW 9/37</t>
+          <t>Краска 9/ Очень светлый блонд 60мл 9/</t>
         </is>
       </c>
       <c r="C900" s="8" t="n">
@@ -15023,10 +15023,10 @@
       </c>
       <c r="E900" s="24" t="n"/>
     </row>
-    <row r="901">
+    <row r="901" ht="22.5" customHeight="1">
       <c r="B901" s="7" t="inlineStr">
         <is>
-          <t>Краска 9/43 Очень светлый блонд красно-коричневый 60мл 9/43</t>
+          <t>Краска 9/03 Очень светлый блонд натуральный золотистый 60мл 9/03</t>
         </is>
       </c>
       <c r="C901" s="8" t="n">
@@ -15042,7 +15042,7 @@
     <row r="902">
       <c r="B902" s="7" t="inlineStr">
         <is>
-          <t>Краска 9/59 Очень светлый блонд махагоновый сандрэ 60мл 9/59</t>
+          <t>Краска 9/19 Очень светлый блонд пепельный сандрэ 60мл 9/19</t>
         </is>
       </c>
       <c r="C902" s="8" t="n">
@@ -15055,10 +15055,10 @@
       </c>
       <c r="E902" s="24" t="n"/>
     </row>
-    <row r="903">
+    <row r="903" ht="22.5" customHeight="1">
       <c r="B903" s="7" t="inlineStr">
         <is>
-          <t>Краска 9/60 Очень светлый фиолетовый натуральный 60мл 9/60</t>
+          <t>Краска 9/37 Очень светлый блонд золотисто-коричневый 60мл NEW 9/37</t>
         </is>
       </c>
       <c r="C903" s="8" t="n">
@@ -15071,88 +15071,88 @@
       </c>
       <c r="E903" s="24" t="n"/>
     </row>
-    <row r="904" ht="14.25" customHeight="1">
-      <c r="B904" s="12" t="inlineStr">
+    <row r="904">
+      <c r="B904" s="7" t="inlineStr">
+        <is>
+          <t>Краска 9/43 Очень светлый блонд красно-коричневый 60мл 9/43</t>
+        </is>
+      </c>
+      <c r="C904" s="8" t="n">
+        <v>759</v>
+      </c>
+      <c r="D904" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E904" s="24" t="n"/>
+    </row>
+    <row r="905">
+      <c r="B905" s="7" t="inlineStr">
+        <is>
+          <t>Краска 9/59 Очень светлый блонд махагоновый сандрэ 60мл 9/59</t>
+        </is>
+      </c>
+      <c r="C905" s="8" t="n">
+        <v>759</v>
+      </c>
+      <c r="D905" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E905" s="24" t="n"/>
+    </row>
+    <row r="906">
+      <c r="B906" s="7" t="inlineStr">
+        <is>
+          <t>Краска 9/60 Очень светлый фиолетовый натуральный 60мл 9/60</t>
+        </is>
+      </c>
+      <c r="C906" s="8" t="n">
+        <v>759</v>
+      </c>
+      <c r="D906" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E906" s="24" t="n"/>
+    </row>
+    <row r="907" ht="14.25" customHeight="1">
+      <c r="B907" s="12" t="inlineStr">
         <is>
           <t>INVIGO - Уход</t>
         </is>
       </c>
-      <c r="C904" s="17" t="n"/>
-      <c r="D904" s="22" t="n"/>
-      <c r="E904" s="22" t="n"/>
-    </row>
-    <row r="905" ht="22.5" customHeight="1">
-      <c r="B905" s="7" t="inlineStr">
+      <c r="C907" s="17" t="n"/>
+      <c r="D907" s="22" t="n"/>
+      <c r="E907" s="22" t="n"/>
+    </row>
+    <row r="908" ht="22.5" customHeight="1">
+      <c r="B908" s="7" t="inlineStr">
         <is>
           <t>Brilliance Бальзам-уход д/защиты цвета окр.жестк.волос 1000мл 339313</t>
         </is>
       </c>
-      <c r="C905" s="10" t="n">
+      <c r="C908" s="10" t="n">
         <v>2824.55</v>
       </c>
-      <c r="D905" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E905" s="24" t="n"/>
-    </row>
-    <row r="906" ht="22.5" customHeight="1">
-      <c r="B906" s="7" t="inlineStr">
+      <c r="D908" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E908" s="24" t="n"/>
+    </row>
+    <row r="909" ht="22.5" customHeight="1">
+      <c r="B909" s="7" t="inlineStr">
         <is>
           <t>Brilliance Бальзам-уход д/защиты цвета окр.жестк.волос 200мл 339252</t>
         </is>
       </c>
-      <c r="C906" s="8" t="n">
+      <c r="C909" s="8" t="n">
         <v>998.75</v>
-      </c>
-      <c r="D906" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E906" s="24" t="n"/>
-    </row>
-    <row r="907" ht="22.5" customHeight="1">
-      <c r="B907" s="7" t="inlineStr">
-        <is>
-          <t>Brilliance Бальзам-уход д/защиты цвета окр.норм.и тонких волос 1000мл 339306</t>
-        </is>
-      </c>
-      <c r="C907" s="10" t="n">
-        <v>2824.55</v>
-      </c>
-      <c r="D907" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E907" s="24" t="n"/>
-    </row>
-    <row r="908">
-      <c r="B908" s="7" t="inlineStr">
-        <is>
-          <t>Brilliance Шампунь д/защиты цвета окр.жестк.волос 1000мл 339290</t>
-        </is>
-      </c>
-      <c r="C908" s="10" t="n">
-        <v>2047.48</v>
-      </c>
-      <c r="D908" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E908" s="24" t="n"/>
-    </row>
-    <row r="909">
-      <c r="B909" s="7" t="inlineStr">
-        <is>
-          <t>Brilliance Шампунь д/защиты цвета окр.жестк.волос 300мл 339238</t>
-        </is>
-      </c>
-      <c r="C909" s="8" t="n">
-        <v>919.7</v>
       </c>
       <c r="D909" s="23" t="inlineStr">
         <is>
@@ -15164,27 +15164,27 @@
     <row r="910" ht="22.5" customHeight="1">
       <c r="B910" s="7" t="inlineStr">
         <is>
-          <t>Brilliance Шампунь д/защиты цвета окр.норм. и тонких волос 1000мл 339283</t>
+          <t>Brilliance Бальзам-уход д/защиты цвета окр.норм.и тонких волос 1000мл 339306</t>
         </is>
       </c>
       <c r="C910" s="10" t="n">
+        <v>2824.55</v>
+      </c>
+      <c r="D910" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E910" s="24" t="n"/>
+    </row>
+    <row r="911">
+      <c r="B911" s="7" t="inlineStr">
+        <is>
+          <t>Brilliance Шампунь д/защиты цвета окр.жестк.волос 1000мл 339290</t>
+        </is>
+      </c>
+      <c r="C911" s="10" t="n">
         <v>2047.48</v>
-      </c>
-      <c r="D910" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E910" s="24" t="n"/>
-    </row>
-    <row r="911" ht="22.5" customHeight="1">
-      <c r="B911" s="7" t="inlineStr">
-        <is>
-          <t>Brilliance Шампунь д/защиты цвета окр.норм. и тонких волос 300мл 339221</t>
-        </is>
-      </c>
-      <c r="C911" s="8" t="n">
-        <v>919.7</v>
       </c>
       <c r="D911" s="23" t="inlineStr">
         <is>
@@ -15196,87 +15196,87 @@
     <row r="912">
       <c r="B912" s="7" t="inlineStr">
         <is>
+          <t>Brilliance Шампунь д/защиты цвета окр.жестк.волос 300мл 339238</t>
+        </is>
+      </c>
+      <c r="C912" s="8" t="n">
+        <v>919.7</v>
+      </c>
+      <c r="D912" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E912" s="24" t="n"/>
+    </row>
+    <row r="913" ht="22.5" customHeight="1">
+      <c r="B913" s="7" t="inlineStr">
+        <is>
+          <t>Brilliance Шампунь д/защиты цвета окр.норм. и тонких волос 1000мл 339283</t>
+        </is>
+      </c>
+      <c r="C913" s="10" t="n">
+        <v>2047.48</v>
+      </c>
+      <c r="D913" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E913" s="24" t="n"/>
+    </row>
+    <row r="914" ht="22.5" customHeight="1">
+      <c r="B914" s="7" t="inlineStr">
+        <is>
+          <t>Brilliance Шампунь д/защиты цвета окр.норм. и тонких волос 300мл 339221</t>
+        </is>
+      </c>
+      <c r="C914" s="8" t="n">
+        <v>919.7</v>
+      </c>
+      <c r="D914" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E914" s="24" t="n"/>
+    </row>
+    <row r="915">
+      <c r="B915" s="7" t="inlineStr">
+        <is>
           <t>ENRICH Крем-бальзам питательный НЕСМЫВАЕМЫЙ 150мл 585659</t>
         </is>
       </c>
-      <c r="C912" s="10" t="n">
+      <c r="C915" s="10" t="n">
         <v>1194.25</v>
       </c>
-      <c r="D912" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E912" s="24" t="n"/>
-    </row>
-    <row r="913">
-      <c r="B913" s="7" t="inlineStr">
+      <c r="D915" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E915" s="24" t="n"/>
+    </row>
+    <row r="916">
+      <c r="B916" s="7" t="inlineStr">
         <is>
           <t>ENRICH Шампунь ультрапитательный 300мл 585765</t>
         </is>
       </c>
-      <c r="C913" s="8" t="n">
+      <c r="C916" s="8" t="n">
         <v>897.6</v>
       </c>
-      <c r="D913" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E913" s="24" t="n"/>
-    </row>
-    <row r="914">
-      <c r="B914" s="25" t="inlineStr">
-        <is>
-          <t>Дозатор д/WELLAPLEX 500 мл. 012341</t>
-        </is>
-      </c>
-      <c r="C914" s="26" t="n">
-        <v>212.5</v>
-      </c>
-      <c r="D914" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E914" s="28" t="n"/>
-    </row>
-    <row r="915">
-      <c r="B915" s="25" t="inlineStr">
-        <is>
-          <t>Дозатор д/кондиционера SYSTEM 271484 85282</t>
-        </is>
-      </c>
-      <c r="C915" s="26" t="n">
-        <v>212.5</v>
-      </c>
-      <c r="D915" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E915" s="28" t="n"/>
-    </row>
-    <row r="916">
-      <c r="B916" s="25" t="inlineStr">
-        <is>
-          <t>Дозатор д/маски 500 мл. 104509</t>
-        </is>
-      </c>
-      <c r="C916" s="26" t="n">
-        <v>212.5</v>
-      </c>
-      <c r="D916" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E916" s="28" t="n"/>
+      <c r="D916" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E916" s="24" t="n"/>
     </row>
     <row r="917">
       <c r="B917" s="25" t="inlineStr">
         <is>
-          <t>Дозатор д/шампуней 1000 мл. 99350093395</t>
+          <t>Дозатор д/WELLAPLEX 500 мл. 012341</t>
         </is>
       </c>
       <c r="C917" s="26" t="n">
@@ -15292,7 +15292,7 @@
     <row r="918">
       <c r="B918" s="25" t="inlineStr">
         <is>
-          <t>Дозатор д/шампуней 500 мл. 034916</t>
+          <t>Дозатор д/кондиционера SYSTEM 271484 85282</t>
         </is>
       </c>
       <c r="C918" s="26" t="n">
@@ -15305,88 +15305,88 @@
       </c>
       <c r="E918" s="28" t="n"/>
     </row>
-    <row r="919" ht="14.25" customHeight="1">
-      <c r="B919" s="12" t="inlineStr">
-        <is>
-          <t>KP Me+/CT - Красители и специальные продукты</t>
-        </is>
-      </c>
-      <c r="C919" s="17" t="n"/>
-      <c r="D919" s="22" t="n"/>
-      <c r="E919" s="22" t="n"/>
+    <row r="919">
+      <c r="B919" s="25" t="inlineStr">
+        <is>
+          <t>Дозатор д/маски 500 мл. 104509</t>
+        </is>
+      </c>
+      <c r="C919" s="26" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="D919" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E919" s="28" t="n"/>
     </row>
     <row r="920">
       <c r="B920" s="25" t="inlineStr">
         <is>
+          <t>Дозатор д/шампуней 1000 мл. 99350093395</t>
+        </is>
+      </c>
+      <c r="C920" s="26" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="D920" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E920" s="28" t="n"/>
+    </row>
+    <row r="921">
+      <c r="B921" s="25" t="inlineStr">
+        <is>
+          <t>Дозатор д/шампуней 500 мл. 034916</t>
+        </is>
+      </c>
+      <c r="C921" s="26" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="D921" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E921" s="28" t="n"/>
+    </row>
+    <row r="922" ht="14.25" customHeight="1">
+      <c r="B922" s="12" t="inlineStr">
+        <is>
+          <t>KP Me+/CT - Красители и специальные продукты</t>
+        </is>
+      </c>
+      <c r="C922" s="17" t="n"/>
+      <c r="D922" s="22" t="n"/>
+      <c r="E922" s="22" t="n"/>
+    </row>
+    <row r="923">
+      <c r="B923" s="25" t="inlineStr">
+        <is>
           <t>Блондирующий крем масленный 7+ 200 мл 6289/x9225</t>
         </is>
       </c>
-      <c r="C920" s="29" t="n">
+      <c r="C923" s="29" t="n">
         <v>1242.11</v>
       </c>
-      <c r="D920" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E920" s="28" t="n"/>
-    </row>
-    <row r="921" ht="22.5" customHeight="1">
-      <c r="B921" s="7" t="inlineStr">
+      <c r="D923" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E923" s="28" t="n"/>
+    </row>
+    <row r="924" ht="22.5" customHeight="1">
+      <c r="B924" s="7" t="inlineStr">
         <is>
           <t>Блондор "BLONDORPLEX" 9+ без образования пыли 800г 99350057291</t>
         </is>
       </c>
-      <c r="C921" s="10" t="n">
+      <c r="C924" s="10" t="n">
         <v>3231</v>
-      </c>
-      <c r="D921" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E921" s="24" t="n"/>
-    </row>
-    <row r="922">
-      <c r="B922" s="7" t="inlineStr">
-        <is>
-          <t>Блондор "FREELIGHTS" пудра 400г 6445/2108/9805</t>
-        </is>
-      </c>
-      <c r="C922" s="10" t="n">
-        <v>2283</v>
-      </c>
-      <c r="D922" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E922" s="24" t="n"/>
-    </row>
-    <row r="923" ht="22.5" customHeight="1">
-      <c r="B923" s="25" t="inlineStr">
-        <is>
-          <t>Блондор "MULTI BLONDE" 7+ порошок осветяющий 800г 6858/99240008189</t>
-        </is>
-      </c>
-      <c r="C923" s="29" t="n">
-        <v>2300.36</v>
-      </c>
-      <c r="D923" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E923" s="28" t="n"/>
-    </row>
-    <row r="924">
-      <c r="B924" s="7" t="inlineStr">
-        <is>
-          <t>Краска CT 10-05 блонд натуральный махагоновый ct10-05</t>
-        </is>
-      </c>
-      <c r="C924" s="8" t="n">
-        <v>715</v>
       </c>
       <c r="D924" s="23" t="inlineStr">
         <is>
@@ -15398,71 +15398,71 @@
     <row r="925">
       <c r="B925" s="7" t="inlineStr">
         <is>
+          <t>Блондор "FREELIGHTS" пудра 400г 6445/2108/9805</t>
+        </is>
+      </c>
+      <c r="C925" s="10" t="n">
+        <v>2283</v>
+      </c>
+      <c r="D925" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E925" s="24" t="n"/>
+    </row>
+    <row r="926" ht="22.5" customHeight="1">
+      <c r="B926" s="25" t="inlineStr">
+        <is>
+          <t>Блондор "MULTI BLONDE" 7+ порошок осветяющий 800г 6858/99240008189</t>
+        </is>
+      </c>
+      <c r="C926" s="29" t="n">
+        <v>2300.36</v>
+      </c>
+      <c r="D926" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E926" s="28" t="n"/>
+    </row>
+    <row r="927">
+      <c r="B927" s="7" t="inlineStr">
+        <is>
+          <t>Краска CT 10-05 блонд натуральный махагоновый ct10-05</t>
+        </is>
+      </c>
+      <c r="C927" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="D927" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E927" s="24" t="n"/>
+    </row>
+    <row r="928">
+      <c r="B928" s="7" t="inlineStr">
+        <is>
           <t>Краска CT 10-1 яркий блондин пепельный ct10-1</t>
         </is>
       </c>
-      <c r="C925" s="8" t="n">
+      <c r="C928" s="8" t="n">
         <v>715</v>
       </c>
-      <c r="D925" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E925" s="24" t="n"/>
-    </row>
-    <row r="926">
-      <c r="B926" s="25" t="inlineStr">
-        <is>
-          <t>Краска CT 10-6 розовая карамель ct10-6</t>
-        </is>
-      </c>
-      <c r="C926" s="26" t="n">
-        <v>664.95</v>
-      </c>
-      <c r="D926" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E926" s="28" t="n"/>
-    </row>
-    <row r="927">
-      <c r="B927" s="25" t="inlineStr">
-        <is>
-          <t>Краска CT 10-81 нежный ангел ct10-81</t>
-        </is>
-      </c>
-      <c r="C927" s="26" t="n">
-        <v>664.95</v>
-      </c>
-      <c r="D927" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E927" s="28" t="n"/>
-    </row>
-    <row r="928">
-      <c r="B928" s="25" t="inlineStr">
-        <is>
-          <t>Краска CT 2-0 черный ct2-0</t>
-        </is>
-      </c>
-      <c r="C928" s="26" t="n">
-        <v>664.95</v>
-      </c>
-      <c r="D928" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E928" s="28" t="n"/>
+      <c r="D928" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E928" s="24" t="n"/>
     </row>
     <row r="929">
       <c r="B929" s="25" t="inlineStr">
         <is>
-          <t>Краска CT 4-0 средне-коричневый ct4-0</t>
+          <t>Краска CT 10-6 розовая карамель ct10-6</t>
         </is>
       </c>
       <c r="C929" s="26" t="n">
@@ -15476,41 +15476,41 @@
       <c r="E929" s="28" t="n"/>
     </row>
     <row r="930">
-      <c r="B930" s="7" t="inlineStr">
-        <is>
-          <t>Краска CT 4-71 коричнево-пепельный ct4-71</t>
-        </is>
-      </c>
-      <c r="C930" s="8" t="n">
-        <v>715</v>
-      </c>
-      <c r="D930" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E930" s="24" t="n"/>
+      <c r="B930" s="25" t="inlineStr">
+        <is>
+          <t>Краска CT 10-81 нежный ангел ct10-81</t>
+        </is>
+      </c>
+      <c r="C930" s="26" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="D930" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E930" s="28" t="n"/>
     </row>
     <row r="931">
-      <c r="B931" s="7" t="inlineStr">
-        <is>
-          <t>Краска CT 4-77 горячий шоколад ct4-77</t>
-        </is>
-      </c>
-      <c r="C931" s="8" t="n">
-        <v>715</v>
-      </c>
-      <c r="D931" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E931" s="24" t="n"/>
+      <c r="B931" s="25" t="inlineStr">
+        <is>
+          <t>Краска CT 2-0 черный ct2-0</t>
+        </is>
+      </c>
+      <c r="C931" s="26" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="D931" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E931" s="28" t="n"/>
     </row>
     <row r="932">
       <c r="B932" s="25" t="inlineStr">
         <is>
-          <t>Краска CT 5-0 светло-коричневый ct5-0</t>
+          <t>Краска CT 4-0 средне-коричневый ct4-0</t>
         </is>
       </c>
       <c r="C932" s="26" t="n">
@@ -15526,7 +15526,7 @@
     <row r="933">
       <c r="B933" s="7" t="inlineStr">
         <is>
-          <t>Краска CT 5-3 светло-коричневый золотистый ct5-3</t>
+          <t>Краска CT 4-71 коричнево-пепельный ct4-71</t>
         </is>
       </c>
       <c r="C933" s="8" t="n">
@@ -15542,7 +15542,7 @@
     <row r="934">
       <c r="B934" s="7" t="inlineStr">
         <is>
-          <t>Краска CT 5-71 грильяж ct5-71</t>
+          <t>Краска CT 4-77 горячий шоколад ct4-77</t>
         </is>
       </c>
       <c r="C934" s="8" t="n">
@@ -15556,41 +15556,41 @@
       <c r="E934" s="24" t="n"/>
     </row>
     <row r="935">
-      <c r="B935" s="7" t="inlineStr">
-        <is>
-          <t>Краска CT 5-75** светло-коричневый махагон ct5-75</t>
-        </is>
-      </c>
-      <c r="C935" s="8" t="n">
+      <c r="B935" s="25" t="inlineStr">
+        <is>
+          <t>Краска CT 5-0 светло-коричневый ct5-0</t>
+        </is>
+      </c>
+      <c r="C935" s="26" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="D935" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E935" s="28" t="n"/>
+    </row>
+    <row r="936">
+      <c r="B936" s="7" t="inlineStr">
+        <is>
+          <t>Краска CT 5-3 светло-коричневый золотистый ct5-3</t>
+        </is>
+      </c>
+      <c r="C936" s="8" t="n">
         <v>715</v>
       </c>
-      <c r="D935" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E935" s="24" t="n"/>
-    </row>
-    <row r="936">
-      <c r="B936" s="25" t="inlineStr">
-        <is>
-          <t>Краска CT 6-0 темный блондин ct6-0</t>
-        </is>
-      </c>
-      <c r="C936" s="26" t="n">
-        <v>664.95</v>
-      </c>
-      <c r="D936" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E936" s="28" t="n"/>
+      <c r="D936" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E936" s="24" t="n"/>
     </row>
     <row r="937">
       <c r="B937" s="7" t="inlineStr">
         <is>
-          <t>краска CT 6-45 глубокий темно-русый красно-махагоновый CT6-45</t>
+          <t>Краска CT 5-71 грильяж ct5-71</t>
         </is>
       </c>
       <c r="C937" s="8" t="n">
@@ -15606,7 +15606,7 @@
     <row r="938">
       <c r="B938" s="7" t="inlineStr">
         <is>
-          <t>Краска CT 6-7 темный блонд коричневый ct6-7</t>
+          <t>Краска CT 5-75** светло-коричневый махагон ct5-75</t>
         </is>
       </c>
       <c r="C938" s="8" t="n">
@@ -15620,57 +15620,57 @@
       <c r="E938" s="24" t="n"/>
     </row>
     <row r="939">
-      <c r="B939" s="7" t="inlineStr">
-        <is>
-          <t>Краска CT 6-73 темный блондин коричнево-золотистый ct6-73</t>
-        </is>
-      </c>
-      <c r="C939" s="8" t="n">
+      <c r="B939" s="25" t="inlineStr">
+        <is>
+          <t>Краска CT 6-0 темный блондин ct6-0</t>
+        </is>
+      </c>
+      <c r="C939" s="26" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="D939" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E939" s="28" t="n"/>
+    </row>
+    <row r="940">
+      <c r="B940" s="7" t="inlineStr">
+        <is>
+          <t>краска CT 6-45 глубокий темно-русый красно-махагоновый CT6-45</t>
+        </is>
+      </c>
+      <c r="C940" s="8" t="n">
         <v>715</v>
       </c>
-      <c r="D939" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E939" s="24" t="n"/>
-    </row>
-    <row r="940">
-      <c r="B940" s="25" t="inlineStr">
-        <is>
-          <t>Краска CT 6-77 кофе со сливками ct6-77</t>
-        </is>
-      </c>
-      <c r="C940" s="26" t="n">
-        <v>664.95</v>
-      </c>
-      <c r="D940" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E940" s="28" t="n"/>
+      <c r="D940" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E940" s="24" t="n"/>
     </row>
     <row r="941">
-      <c r="B941" s="25" t="inlineStr">
-        <is>
-          <t>Краска CT 7-0 средний блондин ct7-0</t>
-        </is>
-      </c>
-      <c r="C941" s="26" t="n">
-        <v>664.95</v>
-      </c>
-      <c r="D941" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E941" s="28" t="n"/>
+      <c r="B941" s="7" t="inlineStr">
+        <is>
+          <t>Краска CT 6-7 темный блонд коричневый ct6-7</t>
+        </is>
+      </c>
+      <c r="C941" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="D941" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E941" s="24" t="n"/>
     </row>
     <row r="942">
       <c r="B942" s="7" t="inlineStr">
         <is>
-          <t>Краска CT 7-1 средне-русый пепельный ct7-1</t>
+          <t>Краска CT 6-73 темный блондин коричнево-золотистый ct6-73</t>
         </is>
       </c>
       <c r="C942" s="8" t="n">
@@ -15684,25 +15684,25 @@
       <c r="E942" s="24" t="n"/>
     </row>
     <row r="943">
-      <c r="B943" s="7" t="inlineStr">
-        <is>
-          <t>Краска CT 7-43 красный тициан ct7-43</t>
-        </is>
-      </c>
-      <c r="C943" s="8" t="n">
-        <v>715</v>
-      </c>
-      <c r="D943" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E943" s="24" t="n"/>
+      <c r="B943" s="25" t="inlineStr">
+        <is>
+          <t>Краска CT 6-77 кофе со сливками ct6-77</t>
+        </is>
+      </c>
+      <c r="C943" s="26" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="D943" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E943" s="28" t="n"/>
     </row>
     <row r="944">
       <c r="B944" s="25" t="inlineStr">
         <is>
-          <t>Краска CT 7-7 цвет косули ct7-7</t>
+          <t>Краска CT 7-0 средний блондин ct7-0</t>
         </is>
       </c>
       <c r="C944" s="26" t="n">
@@ -15718,7 +15718,7 @@
     <row r="945">
       <c r="B945" s="7" t="inlineStr">
         <is>
-          <t>Краска CT 7-71 янтарная куница ct7-71</t>
+          <t>Краска CT 7-1 средне-русый пепельный ct7-1</t>
         </is>
       </c>
       <c r="C945" s="8" t="n">
@@ -15732,25 +15732,25 @@
       <c r="E945" s="24" t="n"/>
     </row>
     <row r="946">
-      <c r="B946" s="25" t="inlineStr">
-        <is>
-          <t>Краска CT 7-73 средний блондин коричнево-золотистый ct7-73</t>
-        </is>
-      </c>
-      <c r="C946" s="26" t="n">
-        <v>664.95</v>
-      </c>
-      <c r="D946" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E946" s="28" t="n"/>
+      <c r="B946" s="7" t="inlineStr">
+        <is>
+          <t>Краска CT 7-43 красный тициан ct7-43</t>
+        </is>
+      </c>
+      <c r="C946" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="D946" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E946" s="24" t="n"/>
     </row>
     <row r="947">
       <c r="B947" s="25" t="inlineStr">
         <is>
-          <t>Краска  CT7-75 светлый палисандр ct7-75</t>
+          <t>Краска CT 7-7 цвет косули ct7-7</t>
         </is>
       </c>
       <c r="C947" s="26" t="n">
@@ -15764,41 +15764,41 @@
       <c r="E947" s="28" t="n"/>
     </row>
     <row r="948">
-      <c r="B948" s="25" t="inlineStr">
-        <is>
-          <t>Краска CT 7-86 блонд жемчужно-фиолетовый ct7-86</t>
-        </is>
-      </c>
-      <c r="C948" s="26" t="n">
+      <c r="B948" s="7" t="inlineStr">
+        <is>
+          <t>Краска CT 7-71 янтарная куница ct7-71</t>
+        </is>
+      </c>
+      <c r="C948" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="D948" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E948" s="24" t="n"/>
+    </row>
+    <row r="949">
+      <c r="B949" s="25" t="inlineStr">
+        <is>
+          <t>Краска CT 7-73 средний блондин коричнево-золотистый ct7-73</t>
+        </is>
+      </c>
+      <c r="C949" s="26" t="n">
         <v>664.95</v>
       </c>
-      <c r="D948" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E948" s="28" t="n"/>
-    </row>
-    <row r="949">
-      <c r="B949" s="7" t="inlineStr">
-        <is>
-          <t>Краска  CT7-89 серый жемчуг ct7-89</t>
-        </is>
-      </c>
-      <c r="C949" s="8" t="n">
-        <v>715</v>
-      </c>
-      <c r="D949" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E949" s="24" t="n"/>
+      <c r="D949" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E949" s="28" t="n"/>
     </row>
     <row r="950">
       <c r="B950" s="25" t="inlineStr">
         <is>
-          <t>Краска CT 7-97 блонд сандре коричневый ct7-97</t>
+          <t>Краска  CT7-75 светлый палисандр ct7-75</t>
         </is>
       </c>
       <c r="C950" s="26" t="n">
@@ -15814,7 +15814,7 @@
     <row r="951">
       <c r="B951" s="25" t="inlineStr">
         <is>
-          <t>Краска CT 8-0 светлый блондин ct8-0</t>
+          <t>Краска CT 7-86 блонд жемчужно-фиолетовый ct7-86</t>
         </is>
       </c>
       <c r="C951" s="26" t="n">
@@ -15830,7 +15830,7 @@
     <row r="952">
       <c r="B952" s="7" t="inlineStr">
         <is>
-          <t>Краска CT 8-38 светлый блонд золотой жемчуг ct8-38</t>
+          <t>Краска  CT7-89 серый жемчуг ct7-89</t>
         </is>
       </c>
       <c r="C952" s="8" t="n">
@@ -15844,25 +15844,25 @@
       <c r="E952" s="24" t="n"/>
     </row>
     <row r="953">
-      <c r="B953" s="7" t="inlineStr">
-        <is>
-          <t>Краска CT 8-41 светлый блонд красно-пепельный ct8-41</t>
-        </is>
-      </c>
-      <c r="C953" s="8" t="n">
-        <v>715</v>
-      </c>
-      <c r="D953" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E953" s="24" t="n"/>
+      <c r="B953" s="25" t="inlineStr">
+        <is>
+          <t>Краска CT 7-97 блонд сандре коричневый ct7-97</t>
+        </is>
+      </c>
+      <c r="C953" s="26" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="D953" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E953" s="28" t="n"/>
     </row>
     <row r="954">
       <c r="B954" s="25" t="inlineStr">
         <is>
-          <t>Краска CT 8-43 боярышник ct8-43</t>
+          <t>Краска CT 8-0 светлый блондин ct8-0</t>
         </is>
       </c>
       <c r="C954" s="26" t="n">
@@ -15876,57 +15876,57 @@
       <c r="E954" s="28" t="n"/>
     </row>
     <row r="955">
-      <c r="B955" s="25" t="inlineStr">
-        <is>
-          <t>Краска CT 8-73 светлый блондин коричнево-золотистый ct8-73</t>
-        </is>
-      </c>
-      <c r="C955" s="26" t="n">
+      <c r="B955" s="7" t="inlineStr">
+        <is>
+          <t>Краска CT 8-38 светлый блонд золотой жемчуг ct8-38</t>
+        </is>
+      </c>
+      <c r="C955" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="D955" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E955" s="24" t="n"/>
+    </row>
+    <row r="956">
+      <c r="B956" s="7" t="inlineStr">
+        <is>
+          <t>Краска CT 8-41 светлый блонд красно-пепельный ct8-41</t>
+        </is>
+      </c>
+      <c r="C956" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="D956" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E956" s="24" t="n"/>
+    </row>
+    <row r="957">
+      <c r="B957" s="25" t="inlineStr">
+        <is>
+          <t>Краска CT 8-43 боярышник ct8-43</t>
+        </is>
+      </c>
+      <c r="C957" s="26" t="n">
         <v>664.95</v>
       </c>
-      <c r="D955" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E955" s="28" t="n"/>
-    </row>
-    <row r="956">
-      <c r="B956" s="25" t="inlineStr">
-        <is>
-          <t>Краска CT 8-81 светлый блондин коричнево-золотистый ct8-81</t>
-        </is>
-      </c>
-      <c r="C956" s="26" t="n">
-        <v>664.95</v>
-      </c>
-      <c r="D956" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E956" s="28" t="n"/>
-    </row>
-    <row r="957">
-      <c r="B957" s="7" t="inlineStr">
-        <is>
-          <t>Краска CT 9-0 очень светлый блондин ct9-0</t>
-        </is>
-      </c>
-      <c r="C957" s="8" t="n">
-        <v>715</v>
-      </c>
-      <c r="D957" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E957" s="24" t="n"/>
+      <c r="D957" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E957" s="28" t="n"/>
     </row>
     <row r="958">
       <c r="B958" s="25" t="inlineStr">
         <is>
-          <t>Краска CT 9-01 пепельный блондин ct9-01</t>
+          <t>Краска CT 8-73 светлый блондин коричнево-золотистый ct8-73</t>
         </is>
       </c>
       <c r="C958" s="26" t="n">
@@ -15942,7 +15942,7 @@
     <row r="959">
       <c r="B959" s="25" t="inlineStr">
         <is>
-          <t>Краска CT 9-16 горный хрусталь ct9-16</t>
+          <t>Краска CT 8-81 светлый блондин коричнево-золотистый ct8-81</t>
         </is>
       </c>
       <c r="C959" s="26" t="n">
@@ -15956,57 +15956,57 @@
       <c r="E959" s="28" t="n"/>
     </row>
     <row r="960">
-      <c r="B960" s="25" t="inlineStr">
-        <is>
-          <t>Краска CT 9-36 розовое золото ct9-36</t>
-        </is>
-      </c>
-      <c r="C960" s="26" t="n">
+      <c r="B960" s="7" t="inlineStr">
+        <is>
+          <t>Краска CT 9-0 очень светлый блондин ct9-0</t>
+        </is>
+      </c>
+      <c r="C960" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="D960" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E960" s="24" t="n"/>
+    </row>
+    <row r="961">
+      <c r="B961" s="25" t="inlineStr">
+        <is>
+          <t>Краска CT 9-01 пепельный блондин ct9-01</t>
+        </is>
+      </c>
+      <c r="C961" s="26" t="n">
         <v>664.95</v>
       </c>
-      <c r="D960" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E960" s="28" t="n"/>
-    </row>
-    <row r="961">
-      <c r="B961" s="7" t="inlineStr">
-        <is>
-          <t>Краска CT 9-73 блондин яркий табак ct9-73</t>
-        </is>
-      </c>
-      <c r="C961" s="8" t="n">
-        <v>715</v>
-      </c>
-      <c r="D961" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E961" s="24" t="n"/>
-    </row>
-    <row r="962" ht="22.5" customHeight="1">
-      <c r="B962" s="7" t="inlineStr">
-        <is>
-          <t>Краска CT 9-75 очень светлый блонд коричнево-махагоновый ct9-75</t>
-        </is>
-      </c>
-      <c r="C962" s="8" t="n">
-        <v>715</v>
-      </c>
-      <c r="D962" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E962" s="24" t="n"/>
+      <c r="D961" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E961" s="28" t="n"/>
+    </row>
+    <row r="962">
+      <c r="B962" s="25" t="inlineStr">
+        <is>
+          <t>Краска CT 9-16 горный хрусталь ct9-16</t>
+        </is>
+      </c>
+      <c r="C962" s="26" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="D962" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E962" s="28" t="n"/>
     </row>
     <row r="963">
       <c r="B963" s="25" t="inlineStr">
         <is>
-          <t>Краска CT 9-86 очень светлый блонд жемчужно-фиолетовый ct9-86</t>
+          <t>Краска CT 9-36 розовое золото ct9-36</t>
         </is>
       </c>
       <c r="C963" s="26" t="n">
@@ -16022,7 +16022,7 @@
     <row r="964">
       <c r="B964" s="7" t="inlineStr">
         <is>
-          <t>Краска CT 9-96 очень светлый блонд сандрэ фиолетовый ct9-96</t>
+          <t>Краска CT 9-73 блондин яркий табак ct9-73</t>
         </is>
       </c>
       <c r="C964" s="8" t="n">
@@ -16035,26 +16035,26 @@
       </c>
       <c r="E964" s="24" t="n"/>
     </row>
-    <row r="965">
-      <c r="B965" s="25" t="inlineStr">
-        <is>
-          <t>Краска CT Plus 44-07 сакура ct44-07</t>
-        </is>
-      </c>
-      <c r="C965" s="26" t="n">
-        <v>664.95</v>
-      </c>
-      <c r="D965" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E965" s="28" t="n"/>
+    <row r="965" ht="22.5" customHeight="1">
+      <c r="B965" s="7" t="inlineStr">
+        <is>
+          <t>Краска CT 9-75 очень светлый блонд коричнево-махагоновый ct9-75</t>
+        </is>
+      </c>
+      <c r="C965" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="D965" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E965" s="24" t="n"/>
     </row>
     <row r="966">
       <c r="B966" s="25" t="inlineStr">
         <is>
-          <t>Краска CT Plus 55-07 кедр ct55-07</t>
+          <t>Краска CT 9-86 очень светлый блонд жемчужно-фиолетовый ct9-86</t>
         </is>
       </c>
       <c r="C966" s="26" t="n">
@@ -16068,25 +16068,25 @@
       <c r="E966" s="28" t="n"/>
     </row>
     <row r="967">
-      <c r="B967" s="25" t="inlineStr">
-        <is>
-          <t>Краска CT Plus 66-07 кипарис ct66-07</t>
-        </is>
-      </c>
-      <c r="C967" s="26" t="n">
-        <v>664.95</v>
-      </c>
-      <c r="D967" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E967" s="28" t="n"/>
+      <c r="B967" s="7" t="inlineStr">
+        <is>
+          <t>Краска CT 9-96 очень светлый блонд сандрэ фиолетовый ct9-96</t>
+        </is>
+      </c>
+      <c r="C967" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="D967" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E967" s="24" t="n"/>
     </row>
     <row r="968">
       <c r="B968" s="25" t="inlineStr">
         <is>
-          <t>Краска CT Plus 77-07 олива ct77-07</t>
+          <t>Краска CT Plus 44-07 сакура ct44-07</t>
         </is>
       </c>
       <c r="C968" s="26" t="n">
@@ -16102,7 +16102,7 @@
     <row r="969">
       <c r="B969" s="25" t="inlineStr">
         <is>
-          <t>Краска CT Plus 88-07 платан ct88-07</t>
+          <t>Краска CT Plus 55-07 кедр ct55-07</t>
         </is>
       </c>
       <c r="C969" s="26" t="n">
@@ -16116,57 +16116,57 @@
       <c r="E969" s="28" t="n"/>
     </row>
     <row r="970">
-      <c r="B970" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 0/11 Пепельный интенс. 60 мл 0-11</t>
-        </is>
-      </c>
-      <c r="C970" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D970" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E970" s="24" t="n"/>
+      <c r="B970" s="25" t="inlineStr">
+        <is>
+          <t>Краска CT Plus 66-07 кипарис ct66-07</t>
+        </is>
+      </c>
+      <c r="C970" s="26" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="D970" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E970" s="28" t="n"/>
     </row>
     <row r="971">
-      <c r="B971" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 0/30 Золотистый натуральный 60мл 0-30</t>
-        </is>
-      </c>
-      <c r="C971" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D971" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E971" s="24" t="n"/>
+      <c r="B971" s="25" t="inlineStr">
+        <is>
+          <t>Краска CT Plus 77-07 олива ct77-07</t>
+        </is>
+      </c>
+      <c r="C971" s="26" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="D971" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E971" s="28" t="n"/>
     </row>
     <row r="972">
-      <c r="B972" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 0/33 Золотистый интенсивный 60мл 0-33</t>
-        </is>
-      </c>
-      <c r="C972" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D972" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E972" s="24" t="n"/>
+      <c r="B972" s="25" t="inlineStr">
+        <is>
+          <t>Краска CT Plus 88-07 платан ct88-07</t>
+        </is>
+      </c>
+      <c r="C972" s="26" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="D972" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E972" s="28" t="n"/>
     </row>
     <row r="973">
       <c r="B973" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 0/43 Красный золотистый 60мл 0-43</t>
+          <t>Краска колестон 0/11 Пепельный интенс. 60 мл 0-11</t>
         </is>
       </c>
       <c r="C973" s="8" t="n">
@@ -16182,7 +16182,7 @@
     <row r="974">
       <c r="B974" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 0/44 Красный интенсивный 60мл 0-44</t>
+          <t>Краска колестон 0/30 Золотистый натуральный 60мл 0-30</t>
         </is>
       </c>
       <c r="C974" s="8" t="n">
@@ -16196,41 +16196,41 @@
       <c r="E974" s="24" t="n"/>
     </row>
     <row r="975">
-      <c r="B975" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 0/66 Фиолетовый интенсивный 60мл 0-66</t>
-        </is>
-      </c>
-      <c r="C975" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D975" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E975" s="28" t="n"/>
+      <c r="B975" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 0/33 Золотистый интенсивный 60мл 0-33</t>
+        </is>
+      </c>
+      <c r="C975" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D975" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E975" s="24" t="n"/>
     </row>
     <row r="976">
-      <c r="B976" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 10/0 Яркий блонд 60мл 10-0</t>
-        </is>
-      </c>
-      <c r="C976" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D976" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E976" s="28" t="n"/>
+      <c r="B976" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 0/43 Красный золотистый 60мл 0-43</t>
+        </is>
+      </c>
+      <c r="C976" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D976" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E976" s="24" t="n"/>
     </row>
     <row r="977">
       <c r="B977" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 10/00 Яркий блонд интенсивный 60мл 10-00</t>
+          <t>Краска колестон 0/44 Красный интенсивный 60мл 0-44</t>
         </is>
       </c>
       <c r="C977" s="8" t="n">
@@ -16246,7 +16246,7 @@
     <row r="978">
       <c r="B978" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 10/03 Пшеница60мл 10-03</t>
+          <t>Краска колестон 0/66 Фиолетовый интенсивный 60мл 0-66</t>
         </is>
       </c>
       <c r="C978" s="26" t="n">
@@ -16260,41 +16260,41 @@
       <c r="E978" s="28" t="n"/>
     </row>
     <row r="979">
-      <c r="B979" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 10/04 Бархатное утро 60мл 10-04</t>
-        </is>
-      </c>
-      <c r="C979" s="8" t="n">
+      <c r="B979" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 10/0 Яркий блонд 60мл 10-0</t>
+        </is>
+      </c>
+      <c r="C979" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D979" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E979" s="28" t="n"/>
+    </row>
+    <row r="980">
+      <c r="B980" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 10/00 Яркий блонд интенсивный 60мл 10-00</t>
+        </is>
+      </c>
+      <c r="C980" s="8" t="n">
         <v>699</v>
       </c>
-      <c r="D979" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E979" s="24" t="n"/>
-    </row>
-    <row r="980">
-      <c r="B980" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 10/1 Ванильный лед 60мл 10-1</t>
-        </is>
-      </c>
-      <c r="C980" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D980" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E980" s="28" t="n"/>
+      <c r="D980" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E980" s="24" t="n"/>
     </row>
     <row r="981">
       <c r="B981" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 10/16  Ванильное небо  60мл 10-16</t>
+          <t>Краска колестон 10/03 Пшеница60мл 10-03</t>
         </is>
       </c>
       <c r="C981" s="26" t="n">
@@ -16310,7 +16310,7 @@
     <row r="982">
       <c r="B982" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 10/3 Шампанское 60мл 10-3</t>
+          <t>Краска колестон 10/04 Бархатное утро 60мл 10-04</t>
         </is>
       </c>
       <c r="C982" s="8" t="n">
@@ -16326,7 +16326,7 @@
     <row r="983">
       <c r="B983" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 10/38 Пудровый экрю  60мл 10-38</t>
+          <t>Краска колестон 10/1 Ванильный лед 60мл 10-1</t>
         </is>
       </c>
       <c r="C983" s="26" t="n">
@@ -16342,7 +16342,7 @@
     <row r="984">
       <c r="B984" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 10/8 Сьерра- Невада  60мл 10-8</t>
+          <t>Краска колестон 10/16  Ванильное небо  60мл 10-16</t>
         </is>
       </c>
       <c r="C984" s="26" t="n">
@@ -16356,25 +16356,25 @@
       <c r="E984" s="28" t="n"/>
     </row>
     <row r="985">
-      <c r="B985" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 10/86 Саламанка 60мл 10-86</t>
-        </is>
-      </c>
-      <c r="C985" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D985" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E985" s="28" t="n"/>
+      <c r="B985" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 10/3 Шампанское 60мл 10-3</t>
+        </is>
+      </c>
+      <c r="C985" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D985" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E985" s="24" t="n"/>
     </row>
     <row r="986">
       <c r="B986" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 10/95 Лавандовый джелато  60мл 10-95</t>
+          <t>Краска колестон 10/38 Пудровый экрю  60мл 10-38</t>
         </is>
       </c>
       <c r="C986" s="26" t="n">
@@ -16390,7 +16390,7 @@
     <row r="987">
       <c r="B987" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 10/96 Бланманже  60мл 10-96</t>
+          <t>Краска колестон 10/8 Сьерра- Невада  60мл 10-8</t>
         </is>
       </c>
       <c r="C987" s="26" t="n">
@@ -16406,7 +16406,7 @@
     <row r="988">
       <c r="B988" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 10/97 Самбук 60мл 10-97</t>
+          <t>Краска колестон 10/86 Саламанка 60мл 10-86</t>
         </is>
       </c>
       <c r="C988" s="26" t="n">
@@ -16422,7 +16422,7 @@
     <row r="989">
       <c r="B989" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 12/0 Кунжут 60мл 12-0</t>
+          <t>Краска колестон 10/95 Лавандовый джелато  60мл 10-95</t>
         </is>
       </c>
       <c r="C989" s="26" t="n">
@@ -16438,7 +16438,7 @@
     <row r="990">
       <c r="B990" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 12/1Песочный 60мл 12-1</t>
+          <t>Краска колестон 10/96 Бланманже  60мл 10-96</t>
         </is>
       </c>
       <c r="C990" s="26" t="n">
@@ -16452,25 +16452,25 @@
       <c r="E990" s="28" t="n"/>
     </row>
     <row r="991">
-      <c r="B991" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 12/11 Ракушка 60мл 12-11</t>
-        </is>
-      </c>
-      <c r="C991" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D991" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E991" s="24" t="n"/>
+      <c r="B991" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 10/97 Самбук 60мл 10-97</t>
+        </is>
+      </c>
+      <c r="C991" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D991" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E991" s="28" t="n"/>
     </row>
     <row r="992">
       <c r="B992" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 12/16 Слоновая кость 60мл 12-16</t>
+          <t>Краска колестон 12/0 Кунжут 60мл 12-0</t>
         </is>
       </c>
       <c r="C992" s="26" t="n">
@@ -16486,7 +16486,7 @@
     <row r="993">
       <c r="B993" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 12/81 Белое золото 60мл 12-81</t>
+          <t>Краска колестон 12/1Песочный 60мл 12-1</t>
         </is>
       </c>
       <c r="C993" s="26" t="n">
@@ -16500,25 +16500,25 @@
       <c r="E993" s="28" t="n"/>
     </row>
     <row r="994">
-      <c r="B994" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 12/89 Ванильный  60мл 12-89</t>
-        </is>
-      </c>
-      <c r="C994" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D994" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E994" s="28" t="n"/>
+      <c r="B994" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 12/11 Ракушка 60мл 12-11</t>
+        </is>
+      </c>
+      <c r="C994" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D994" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E994" s="24" t="n"/>
     </row>
     <row r="995">
       <c r="B995" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 12/96 Бежевый иней  60мл 12-96</t>
+          <t>Краска колестон 12/16 Слоновая кость 60мл 12-16</t>
         </is>
       </c>
       <c r="C995" s="26" t="n">
@@ -16534,7 +16534,7 @@
     <row r="996">
       <c r="B996" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 2/0 Черный натуральный 60мл 2-0</t>
+          <t>Краска колестон 12/81 Белое золото 60мл 12-81</t>
         </is>
       </c>
       <c r="C996" s="26" t="n">
@@ -16547,26 +16547,26 @@
       </c>
       <c r="E996" s="28" t="n"/>
     </row>
-    <row r="997" ht="22.5" customHeight="1">
-      <c r="B997" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 3/00 Темно-коричневый интенс. натуральный 60мл 3-00</t>
-        </is>
-      </c>
-      <c r="C997" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D997" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E997" s="24" t="n"/>
+    <row r="997">
+      <c r="B997" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 12/89 Ванильный  60мл 12-89</t>
+        </is>
+      </c>
+      <c r="C997" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D997" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E997" s="28" t="n"/>
     </row>
     <row r="998">
       <c r="B998" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 4/0 Коричневый  натуральный 60мл 4-0</t>
+          <t>Краска колестон 12/96 Бежевый иней  60мл 12-96</t>
         </is>
       </c>
       <c r="C998" s="26" t="n">
@@ -16579,10 +16579,10 @@
       </c>
       <c r="E998" s="28" t="n"/>
     </row>
-    <row r="999" ht="22.5" customHeight="1">
+    <row r="999">
       <c r="B999" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 4/00 Коричневый интенсивный натуральный 60мл 4-00</t>
+          <t>Краска колестон 2/0 Черный натуральный 60мл 2-0</t>
         </is>
       </c>
       <c r="C999" s="26" t="n">
@@ -16595,26 +16595,26 @@
       </c>
       <c r="E999" s="28" t="n"/>
     </row>
-    <row r="1000">
-      <c r="B1000" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 4/07 Сакура 60мл 4-07</t>
-        </is>
-      </c>
-      <c r="C1000" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D1000" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1000" s="28" t="n"/>
+    <row r="1000" ht="22.5" customHeight="1">
+      <c r="B1000" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 3/00 Темно-коричневый интенс. натуральный 60мл 3-00</t>
+        </is>
+      </c>
+      <c r="C1000" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1000" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1000" s="24" t="n"/>
     </row>
     <row r="1001">
       <c r="B1001" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 4/75 Бомбейский палисандр 60мл 4-75</t>
+          <t>Краска колестон 4/0 Коричневый  натуральный 60мл 4-0</t>
         </is>
       </c>
       <c r="C1001" s="26" t="n">
@@ -16627,10 +16627,10 @@
       </c>
       <c r="E1001" s="28" t="n"/>
     </row>
-    <row r="1002">
+    <row r="1002" ht="22.5" customHeight="1">
       <c r="B1002" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 4/77 Горячий шоколад  60мл 4-77</t>
+          <t>Краска колестон 4/00 Коричневый интенсивный натуральный 60мл 4-00</t>
         </is>
       </c>
       <c r="C1002" s="26" t="n">
@@ -16643,10 +16643,10 @@
       </c>
       <c r="E1002" s="28" t="n"/>
     </row>
-    <row r="1003" ht="22.5" customHeight="1">
+    <row r="1003">
       <c r="B1003" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 44/0 Коричневый интенсивный натуральный 60мл 44-0</t>
+          <t>Краска колестон 4/07 Сакура 60мл 4-07</t>
         </is>
       </c>
       <c r="C1003" s="26" t="n">
@@ -16662,7 +16662,7 @@
     <row r="1004">
       <c r="B1004" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 5/0 Светло-коричневый натуральный 60мл 5-0</t>
+          <t>Краска колестон 4/75 Бомбейский палисандр 60мл 4-75</t>
         </is>
       </c>
       <c r="C1004" s="26" t="n">
@@ -16678,7 +16678,7 @@
     <row r="1005">
       <c r="B1005" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 5/00  60мл 5-00</t>
+          <t>Краска колестон 4/77 Горячий шоколад  60мл 4-77</t>
         </is>
       </c>
       <c r="C1005" s="26" t="n">
@@ -16691,58 +16691,58 @@
       </c>
       <c r="E1005" s="28" t="n"/>
     </row>
-    <row r="1006">
-      <c r="B1006" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 5/07 Кедр  60мл 5-07</t>
-        </is>
-      </c>
-      <c r="C1006" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1006" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1006" s="24" t="n"/>
-    </row>
-    <row r="1007" ht="22.5" customHeight="1">
-      <c r="B1007" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 5/1 Светло-коричневый пепельный Шоколадное джелатто  60мл 5-1</t>
-        </is>
-      </c>
-      <c r="C1007" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1007" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1007" s="24" t="n"/>
-    </row>
-    <row r="1008" ht="22.5" customHeight="1">
-      <c r="B1008" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 5/2 Светло-коричневый матовый Итальянская сосна 60мл 5-2</t>
-        </is>
-      </c>
-      <c r="C1008" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1008" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1008" s="24" t="n"/>
+    <row r="1006" ht="22.5" customHeight="1">
+      <c r="B1006" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 44/0 Коричневый интенсивный натуральный 60мл 44-0</t>
+        </is>
+      </c>
+      <c r="C1006" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1006" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1006" s="28" t="n"/>
+    </row>
+    <row r="1007">
+      <c r="B1007" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 5/0 Светло-коричневый натуральный 60мл 5-0</t>
+        </is>
+      </c>
+      <c r="C1007" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1007" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1007" s="28" t="n"/>
+    </row>
+    <row r="1008">
+      <c r="B1008" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 5/00  60мл 5-00</t>
+        </is>
+      </c>
+      <c r="C1008" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1008" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1008" s="28" t="n"/>
     </row>
     <row r="1009">
       <c r="B1009" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 5/3 корич. золотистый 60мл 5-3</t>
+          <t>Краска колестон 5/07 Кедр  60мл 5-07</t>
         </is>
       </c>
       <c r="C1009" s="8" t="n">
@@ -16755,26 +16755,26 @@
       </c>
       <c r="E1009" s="24" t="n"/>
     </row>
-    <row r="1010">
-      <c r="B1010" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 5/71 Грильяж  60мл 5-71</t>
-        </is>
-      </c>
-      <c r="C1010" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D1010" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1010" s="28" t="n"/>
-    </row>
-    <row r="1011">
+    <row r="1010" ht="22.5" customHeight="1">
+      <c r="B1010" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 5/1 Светло-коричневый пепельный Шоколадное джелатто  60мл 5-1</t>
+        </is>
+      </c>
+      <c r="C1010" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1010" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1010" s="24" t="n"/>
+    </row>
+    <row r="1011" ht="22.5" customHeight="1">
       <c r="B1011" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 5/75 Темный палисандр  60мл 5-75</t>
+          <t>Краска колестон 5/2 Светло-коричневый матовый Итальянская сосна 60мл 5-2</t>
         </is>
       </c>
       <c r="C1011" s="8" t="n">
@@ -16788,25 +16788,25 @@
       <c r="E1011" s="24" t="n"/>
     </row>
     <row r="1012">
-      <c r="B1012" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 5/77 Мокко  60мл 5-77</t>
-        </is>
-      </c>
-      <c r="C1012" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D1012" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1012" s="28" t="n"/>
-    </row>
-    <row r="1013" ht="22.5" customHeight="1">
+      <c r="B1012" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 5/3 корич. золотистый 60мл 5-3</t>
+        </is>
+      </c>
+      <c r="C1012" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1012" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1012" s="24" t="n"/>
+    </row>
+    <row r="1013">
       <c r="B1013" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 55/0 Светло-коричневый интенсивный натуральный 60мл 55-0</t>
+          <t>Краска колестон 5/71 Грильяж  60мл 5-71</t>
         </is>
       </c>
       <c r="C1013" s="26" t="n">
@@ -16820,25 +16820,25 @@
       <c r="E1013" s="28" t="n"/>
     </row>
     <row r="1014">
-      <c r="B1014" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 6/0 Темный блонд натуральный 60мл 6-0</t>
-        </is>
-      </c>
-      <c r="C1014" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D1014" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1014" s="28" t="n"/>
+      <c r="B1014" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 5/75 Темный палисандр  60мл 5-75</t>
+        </is>
+      </c>
+      <c r="C1014" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1014" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1014" s="24" t="n"/>
     </row>
     <row r="1015">
       <c r="B1015" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 6/00 Темный блонд натуральный интенс. 60мл 6-00</t>
+          <t>Краска колестон 5/77 Мокко  60мл 5-77</t>
         </is>
       </c>
       <c r="C1015" s="26" t="n">
@@ -16851,26 +16851,26 @@
       </c>
       <c r="E1015" s="28" t="n"/>
     </row>
-    <row r="1016">
-      <c r="B1016" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 6/07 Кипарис 60мл 6-07</t>
-        </is>
-      </c>
-      <c r="C1016" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1016" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1016" s="24" t="n"/>
-    </row>
-    <row r="1017" ht="22.5" customHeight="1">
+    <row r="1016" ht="22.5" customHeight="1">
+      <c r="B1016" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 55/0 Светло-коричневый интенсивный натуральный 60мл 55-0</t>
+        </is>
+      </c>
+      <c r="C1016" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1016" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1016" s="28" t="n"/>
+    </row>
+    <row r="1017">
       <c r="B1017" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 6/1 Темный блонд пепельный Древесный дым 60мл 6-1</t>
+          <t>Краска колестон 6/0 Темный блонд натуральный 60мл 6-0</t>
         </is>
       </c>
       <c r="C1017" s="26" t="n">
@@ -16884,25 +16884,25 @@
       <c r="E1017" s="28" t="n"/>
     </row>
     <row r="1018">
-      <c r="B1018" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 6/34 Медовый пунш 60 мл. 6-34</t>
-        </is>
-      </c>
-      <c r="C1018" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1018" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1018" s="24" t="n"/>
+      <c r="B1018" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 6/00 Темный блонд натуральный интенс. 60мл 6-00</t>
+        </is>
+      </c>
+      <c r="C1018" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1018" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1018" s="28" t="n"/>
     </row>
     <row r="1019">
       <c r="B1019" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 6/41 Мехико 60мл 6-41</t>
+          <t>Краска колестон 6/07 Кипарис 60мл 6-07</t>
         </is>
       </c>
       <c r="C1019" s="8" t="n">
@@ -16915,78 +16915,78 @@
       </c>
       <c r="E1019" s="24" t="n"/>
     </row>
-    <row r="1020">
-      <c r="B1020" s="7" t="inlineStr">
+    <row r="1020" ht="22.5" customHeight="1">
+      <c r="B1020" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 6/1 Темный блонд пепельный Древесный дым 60мл 6-1</t>
+        </is>
+      </c>
+      <c r="C1020" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1020" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1020" s="28" t="n"/>
+    </row>
+    <row r="1021">
+      <c r="B1021" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 6/34 Медовый пунш 60 мл. 6-34</t>
+        </is>
+      </c>
+      <c r="C1021" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1021" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1021" s="24" t="n"/>
+    </row>
+    <row r="1022">
+      <c r="B1022" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 6/41 Мехико 60мл 6-41</t>
+        </is>
+      </c>
+      <c r="C1022" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1022" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1022" s="24" t="n"/>
+    </row>
+    <row r="1023">
+      <c r="B1023" s="7" t="inlineStr">
         <is>
           <t>Краска колестон 6/43 Дикая орхидея  60мл 6-43</t>
         </is>
       </c>
-      <c r="C1020" s="8" t="n">
+      <c r="C1023" s="8" t="n">
         <v>699</v>
       </c>
-      <c r="D1020" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1020" s="24" t="n"/>
-    </row>
-    <row r="1021">
-      <c r="B1021" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 6/7 Эскимо  60мл 6-7</t>
-        </is>
-      </c>
-      <c r="C1021" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D1021" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1021" s="28" t="n"/>
-    </row>
-    <row r="1022">
-      <c r="B1022" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 6/97  Кофейный мусс  60мл 6-97</t>
-        </is>
-      </c>
-      <c r="C1022" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D1022" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1022" s="28" t="n"/>
-    </row>
-    <row r="1023">
-      <c r="B1023" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 66/0 Темный блонд натуральный 60мл 66-0</t>
-        </is>
-      </c>
-      <c r="C1023" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D1023" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1023" s="28" t="n"/>
+      <c r="D1023" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1023" s="24" t="n"/>
     </row>
     <row r="1024">
       <c r="B1024" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 7/0 Блонд натуральный 60мл 7-0</t>
+          <t>Краска колестон 6/7 Эскимо  60мл 6-7</t>
         </is>
       </c>
       <c r="C1024" s="26" t="n">
-        <v>594.15</v>
+        <v>650.0700000000001</v>
       </c>
       <c r="D1024" s="27" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
     <row r="1025">
       <c r="B1025" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 7/00 Блонд натуральный интенс. 60мл 7-00</t>
+          <t>Краска колестон 6/97  Кофейный мусс  60мл 6-97</t>
         </is>
       </c>
       <c r="C1025" s="26" t="n">
@@ -17012,41 +17012,41 @@
       <c r="E1025" s="28" t="n"/>
     </row>
     <row r="1026">
-      <c r="B1026" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 7/01 Фундук 60мл 7-01</t>
-        </is>
-      </c>
-      <c r="C1026" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1026" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1026" s="24" t="n"/>
+      <c r="B1026" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 66/0 Темный блонд натуральный 60мл 66-0</t>
+        </is>
+      </c>
+      <c r="C1026" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1026" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1026" s="28" t="n"/>
     </row>
     <row r="1027">
-      <c r="B1027" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 7/07 Олива  60мл 7-07</t>
-        </is>
-      </c>
-      <c r="C1027" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1027" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1027" s="24" t="n"/>
+      <c r="B1027" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 7/0 Блонд натуральный 60мл 7-0</t>
+        </is>
+      </c>
+      <c r="C1027" s="26" t="n">
+        <v>594.15</v>
+      </c>
+      <c r="D1027" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1027" s="28" t="n"/>
     </row>
     <row r="1028">
       <c r="B1028" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 7/1 Табачный маррон 60мл 7-1</t>
+          <t>Краска колестон 7/00 Блонд натуральный интенс. 60мл 7-00</t>
         </is>
       </c>
       <c r="C1028" s="26" t="n">
@@ -17062,7 +17062,7 @@
     <row r="1029">
       <c r="B1029" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 7/17 Кедровый мистраль 60мл 7-17</t>
+          <t>Краска колестон 7/01 Фундук 60мл 7-01</t>
         </is>
       </c>
       <c r="C1029" s="8" t="n">
@@ -17078,7 +17078,7 @@
     <row r="1030">
       <c r="B1030" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 7/31 Комо 60мл 7-31</t>
+          <t>Краска колестон 7/07 Олива  60мл 7-07</t>
         </is>
       </c>
       <c r="C1030" s="8" t="n">
@@ -17094,7 +17094,7 @@
     <row r="1031">
       <c r="B1031" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 7/36 7-36</t>
+          <t>Краска колестон 7/1 Табачный маррон 60мл 7-1</t>
         </is>
       </c>
       <c r="C1031" s="26" t="n">
@@ -17110,7 +17110,7 @@
     <row r="1032">
       <c r="B1032" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 7/38 Пряный бисквит 60мл 7-38</t>
+          <t>Краска колестон 7/17 Кедровый мистраль 60мл 7-17</t>
         </is>
       </c>
       <c r="C1032" s="8" t="n">
@@ -17124,41 +17124,41 @@
       <c r="E1032" s="24" t="n"/>
     </row>
     <row r="1033">
-      <c r="B1033" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 7/43 Красный тициан 60мл 7-43</t>
-        </is>
-      </c>
-      <c r="C1033" s="26" t="n">
+      <c r="B1033" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 7/31 Комо 60мл 7-31</t>
+        </is>
+      </c>
+      <c r="C1033" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1033" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1033" s="24" t="n"/>
+    </row>
+    <row r="1034">
+      <c r="B1034" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 7/36 7-36</t>
+        </is>
+      </c>
+      <c r="C1034" s="26" t="n">
         <v>650.0700000000001</v>
       </c>
-      <c r="D1033" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1033" s="28" t="n"/>
-    </row>
-    <row r="1034">
-      <c r="B1034" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 7/47 60мл 7-47</t>
-        </is>
-      </c>
-      <c r="C1034" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1034" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1034" s="24" t="n"/>
+      <c r="D1034" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1034" s="28" t="n"/>
     </row>
     <row r="1035">
       <c r="B1035" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 7/77 Блонд коричневый интенсивный 60мл 7-77</t>
+          <t>Краска колестон 7/38 Пряный бисквит 60мл 7-38</t>
         </is>
       </c>
       <c r="C1035" s="8" t="n">
@@ -17174,7 +17174,7 @@
     <row r="1036">
       <c r="B1036" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 77/0 Блонд интенсивный натуральный  60мл 77-0</t>
+          <t>Краска колестон 7/43 Красный тициан 60мл 7-43</t>
         </is>
       </c>
       <c r="C1036" s="26" t="n">
@@ -17188,25 +17188,25 @@
       <c r="E1036" s="28" t="n"/>
     </row>
     <row r="1037">
-      <c r="B1037" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 8/01 Миндаль 60мл 8-01</t>
-        </is>
-      </c>
-      <c r="C1037" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D1037" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1037" s="28" t="n"/>
+      <c r="B1037" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 7/47 60мл 7-47</t>
+        </is>
+      </c>
+      <c r="C1037" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1037" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1037" s="24" t="n"/>
     </row>
     <row r="1038">
       <c r="B1038" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 8/03 Янтарь  60мл 8-03</t>
+          <t>Краска колестон 7/77 Блонд коричневый интенсивный 60мл 7-77</t>
         </is>
       </c>
       <c r="C1038" s="8" t="n">
@@ -17220,25 +17220,25 @@
       <c r="E1038" s="24" t="n"/>
     </row>
     <row r="1039">
-      <c r="B1039" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 8/04 Яркий закат  60мл 8-04</t>
-        </is>
-      </c>
-      <c r="C1039" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1039" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1039" s="24" t="n"/>
+      <c r="B1039" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 77/0 Блонд интенсивный натуральный  60мл 77-0</t>
+        </is>
+      </c>
+      <c r="C1039" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1039" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1039" s="28" t="n"/>
     </row>
     <row r="1040">
       <c r="B1040" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 8/1 Песчаная буря 60мл 8-1</t>
+          <t>Краска колестон 8/01 Миндаль 60мл 8-01</t>
         </is>
       </c>
       <c r="C1040" s="26" t="n">
@@ -17252,89 +17252,89 @@
       <c r="E1040" s="28" t="n"/>
     </row>
     <row r="1041">
-      <c r="B1041" s="25" t="inlineStr">
+      <c r="B1041" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 8/03 Янтарь  60мл 8-03</t>
+        </is>
+      </c>
+      <c r="C1041" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1041" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1041" s="24" t="n"/>
+    </row>
+    <row r="1042">
+      <c r="B1042" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 8/04 Яркий закат  60мл 8-04</t>
+        </is>
+      </c>
+      <c r="C1042" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1042" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1042" s="24" t="n"/>
+    </row>
+    <row r="1043">
+      <c r="B1043" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 8/1 Песчаная буря 60мл 8-1</t>
+        </is>
+      </c>
+      <c r="C1043" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1043" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1043" s="28" t="n"/>
+    </row>
+    <row r="1044">
+      <c r="B1044" s="25" t="inlineStr">
         <is>
           <t>Краска колестон 8/34 Чилийский оранжевый   60мл 8-34</t>
         </is>
       </c>
-      <c r="C1041" s="26" t="n">
+      <c r="C1044" s="26" t="n">
         <v>650.0700000000001</v>
       </c>
-      <c r="D1041" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1041" s="28" t="n"/>
-    </row>
-    <row r="1042">
-      <c r="B1042" s="25" t="inlineStr">
+      <c r="D1044" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1044" s="28" t="n"/>
+    </row>
+    <row r="1045">
+      <c r="B1045" s="25" t="inlineStr">
         <is>
           <t>Краска колестон 8/38 Золотая умбра   60мл 8-38</t>
         </is>
       </c>
-      <c r="C1042" s="26" t="n">
+      <c r="C1045" s="26" t="n">
         <v>650.0700000000001</v>
       </c>
-      <c r="D1042" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1042" s="28" t="n"/>
-    </row>
-    <row r="1043">
-      <c r="B1043" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 8/41 Марракеш 60мл 8-41</t>
-        </is>
-      </c>
-      <c r="C1043" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1043" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1043" s="24" t="n"/>
-    </row>
-    <row r="1044">
-      <c r="B1044" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 8/43 Боярышник   60мл 8-43</t>
-        </is>
-      </c>
-      <c r="C1044" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1044" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1044" s="24" t="n"/>
-    </row>
-    <row r="1045">
-      <c r="B1045" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 8/7 Шоколадный трюфель  60мл 8-7</t>
-        </is>
-      </c>
-      <c r="C1045" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1045" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1045" s="24" t="n"/>
+      <c r="D1045" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1045" s="28" t="n"/>
     </row>
     <row r="1046">
       <c r="B1046" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 8/74 ирландский красный 60мл 8-74</t>
+          <t>Краска колестон 8/41 Марракеш 60мл 8-41</t>
         </is>
       </c>
       <c r="C1046" s="8" t="n">
@@ -17348,25 +17348,25 @@
       <c r="E1046" s="24" t="n"/>
     </row>
     <row r="1047">
-      <c r="B1047" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 8/96 Панакота   60мл 8-96</t>
-        </is>
-      </c>
-      <c r="C1047" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D1047" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1047" s="28" t="n"/>
+      <c r="B1047" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 8/43 Боярышник   60мл 8-43</t>
+        </is>
+      </c>
+      <c r="C1047" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1047" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1047" s="24" t="n"/>
     </row>
     <row r="1048">
       <c r="B1048" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 8/97 Молочный шоколад 60мл 8-97</t>
+          <t>Краска колестон 8/7 Шоколадный трюфель  60мл 8-7</t>
         </is>
       </c>
       <c r="C1048" s="8" t="n">
@@ -17380,89 +17380,89 @@
       <c r="E1048" s="24" t="n"/>
     </row>
     <row r="1049">
-      <c r="B1049" s="25" t="inlineStr">
+      <c r="B1049" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 8/74 ирландский красный 60мл 8-74</t>
+        </is>
+      </c>
+      <c r="C1049" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1049" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1049" s="24" t="n"/>
+    </row>
+    <row r="1050">
+      <c r="B1050" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 8/96 Панакота   60мл 8-96</t>
+        </is>
+      </c>
+      <c r="C1050" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1050" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1050" s="28" t="n"/>
+    </row>
+    <row r="1051">
+      <c r="B1051" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 8/97 Молочный шоколад 60мл 8-97</t>
+        </is>
+      </c>
+      <c r="C1051" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1051" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1051" s="24" t="n"/>
+    </row>
+    <row r="1052">
+      <c r="B1052" s="25" t="inlineStr">
         <is>
           <t>Краска колестон 88/0 Светлый блонд натуральный 60мл 88-0</t>
         </is>
       </c>
-      <c r="C1049" s="26" t="n">
+      <c r="C1052" s="26" t="n">
         <v>650.0700000000001</v>
       </c>
-      <c r="D1049" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1049" s="28" t="n"/>
-    </row>
-    <row r="1050">
-      <c r="B1050" s="7" t="inlineStr">
+      <c r="D1052" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1052" s="28" t="n"/>
+    </row>
+    <row r="1053">
+      <c r="B1053" s="7" t="inlineStr">
         <is>
           <t>Краска колестон 88/43 Ирландское лето   60мл 88-43</t>
         </is>
       </c>
-      <c r="C1050" s="8" t="n">
+      <c r="C1053" s="8" t="n">
         <v>699</v>
       </c>
-      <c r="D1050" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1050" s="24" t="n"/>
-    </row>
-    <row r="1051">
-      <c r="B1051" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 9/0 Очень светлый блонд натуральный 60мл 9-0</t>
-        </is>
-      </c>
-      <c r="C1051" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D1051" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1051" s="28" t="n"/>
-    </row>
-    <row r="1052" ht="22.5" customHeight="1">
-      <c r="B1052" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 9/00 Очень светлый блонд натуральный интенс. 60мл 9-00</t>
-        </is>
-      </c>
-      <c r="C1052" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1052" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1052" s="24" t="n"/>
-    </row>
-    <row r="1053">
-      <c r="B1053" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 9/01 Орех пекан 60мл 9-01</t>
-        </is>
-      </c>
-      <c r="C1053" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D1053" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1053" s="28" t="n"/>
+      <c r="D1053" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1053" s="24" t="n"/>
     </row>
     <row r="1054">
       <c r="B1054" s="25" t="inlineStr">
         <is>
-          <t>Краска колестон 9/03 Лен 60мл 9-03</t>
+          <t>Краска колестон 9/0 Очень светлый блонд натуральный 60мл 9-0</t>
         </is>
       </c>
       <c r="C1054" s="26" t="n">
@@ -17475,106 +17475,106 @@
       </c>
       <c r="E1054" s="28" t="n"/>
     </row>
-    <row r="1055">
-      <c r="B1055" s="25" t="inlineStr">
+    <row r="1055" ht="22.5" customHeight="1">
+      <c r="B1055" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 9/00 Очень светлый блонд натуральный интенс. 60мл 9-00</t>
+        </is>
+      </c>
+      <c r="C1055" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1055" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1055" s="24" t="n"/>
+    </row>
+    <row r="1056">
+      <c r="B1056" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 9/01 Орех пекан 60мл 9-01</t>
+        </is>
+      </c>
+      <c r="C1056" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1056" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1056" s="28" t="n"/>
+    </row>
+    <row r="1057">
+      <c r="B1057" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 9/03 Лен 60мл 9-03</t>
+        </is>
+      </c>
+      <c r="C1057" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1057" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1057" s="28" t="n"/>
+    </row>
+    <row r="1058">
+      <c r="B1058" s="25" t="inlineStr">
         <is>
           <t>Краска колестон 9/1 Кремовое облако 60мл 9-1</t>
         </is>
       </c>
-      <c r="C1055" s="26" t="n">
+      <c r="C1058" s="26" t="n">
         <v>650.0700000000001</v>
       </c>
-      <c r="D1055" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1055" s="28" t="n"/>
-    </row>
-    <row r="1056">
-      <c r="B1056" s="7" t="inlineStr">
+      <c r="D1058" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1058" s="28" t="n"/>
+    </row>
+    <row r="1059">
+      <c r="B1059" s="7" t="inlineStr">
         <is>
           <t>Краска колестон 9/16 Горный хрусталь  60мл 9-16</t>
         </is>
       </c>
-      <c r="C1056" s="8" t="n">
+      <c r="C1059" s="8" t="n">
         <v>699</v>
       </c>
-      <c r="D1056" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1056" s="24" t="n"/>
-    </row>
-    <row r="1057">
-      <c r="B1057" s="7" t="inlineStr">
+      <c r="D1059" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1059" s="24" t="n"/>
+    </row>
+    <row r="1060">
+      <c r="B1060" s="7" t="inlineStr">
         <is>
           <t>Краска колестон 9/17 Шелковый ристретто   60мл 9-17</t>
         </is>
       </c>
-      <c r="C1057" s="8" t="n">
+      <c r="C1060" s="8" t="n">
         <v>699</v>
       </c>
-      <c r="D1057" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1057" s="24" t="n"/>
-    </row>
-    <row r="1058">
-      <c r="B1058" s="7" t="inlineStr">
-        <is>
-          <t>Краска колестон 9/7 Мускатный орех 60мл 9-7</t>
-        </is>
-      </c>
-      <c r="C1058" s="8" t="n">
-        <v>699</v>
-      </c>
-      <c r="D1058" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1058" s="24" t="n"/>
-    </row>
-    <row r="1059">
-      <c r="B1059" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 9/8 Анды  60мл 9-8</t>
-        </is>
-      </c>
-      <c r="C1059" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D1059" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1059" s="28" t="n"/>
-    </row>
-    <row r="1060">
-      <c r="B1060" s="25" t="inlineStr">
-        <is>
-          <t>Краска колестон 9/81 Сливочный камео 60мл 9-81</t>
-        </is>
-      </c>
-      <c r="C1060" s="26" t="n">
-        <v>650.0700000000001</v>
-      </c>
-      <c r="D1060" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1060" s="28" t="n"/>
+      <c r="D1060" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1060" s="24" t="n"/>
     </row>
     <row r="1061">
       <c r="B1061" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 9/97 Айриш крем 60мл 9-97</t>
+          <t>Краска колестон 9/7 Мускатный орех 60мл 9-7</t>
         </is>
       </c>
       <c r="C1061" s="8" t="n">
@@ -17588,73 +17588,73 @@
       <c r="E1061" s="24" t="n"/>
     </row>
     <row r="1062">
-      <c r="B1062" s="7" t="inlineStr">
+      <c r="B1062" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 9/8 Анды  60мл 9-8</t>
+        </is>
+      </c>
+      <c r="C1062" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1062" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1062" s="28" t="n"/>
+    </row>
+    <row r="1063">
+      <c r="B1063" s="25" t="inlineStr">
+        <is>
+          <t>Краска колестон 9/81 Сливочный камео 60мл 9-81</t>
+        </is>
+      </c>
+      <c r="C1063" s="26" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="D1063" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1063" s="28" t="n"/>
+    </row>
+    <row r="1064">
+      <c r="B1064" s="7" t="inlineStr">
+        <is>
+          <t>Краска колестон 9/97 Айриш крем 60мл 9-97</t>
+        </is>
+      </c>
+      <c r="C1064" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="D1064" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1064" s="24" t="n"/>
+    </row>
+    <row r="1065">
+      <c r="B1065" s="7" t="inlineStr">
         <is>
           <t>Краска колестон 99/0 Очень светлый блонд натуральный 60мл 99-0</t>
         </is>
       </c>
-      <c r="C1062" s="8" t="n">
+      <c r="C1065" s="8" t="n">
         <v>699</v>
       </c>
-      <c r="D1062" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1062" s="24" t="n"/>
-    </row>
-    <row r="1063" ht="22.5" customHeight="1">
-      <c r="B1063" s="25" t="inlineStr">
-        <is>
-          <t>Окислитель Welloxon Perfect 1,9% 1000мл ДЛЯ ПАСТЕЛЬНОГО ТОНИРОВАНИЯ 6495/6921</t>
-        </is>
-      </c>
-      <c r="C1063" s="26" t="n">
-        <v>928.6799999999999</v>
-      </c>
-      <c r="D1063" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1063" s="28" t="n"/>
-    </row>
-    <row r="1064">
-      <c r="B1064" s="25" t="inlineStr">
-        <is>
-          <t>Окислитель Welloxon Perfect 12% 1000мл 6499/6488</t>
-        </is>
-      </c>
-      <c r="C1064" s="26" t="n">
-        <v>928.6799999999999</v>
-      </c>
-      <c r="D1064" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1064" s="28" t="n"/>
-    </row>
-    <row r="1065">
-      <c r="B1065" s="25" t="inlineStr">
-        <is>
-          <t>Окислитель Welloxon Perfect 12% 60мл 6494/50931</t>
-        </is>
-      </c>
-      <c r="C1065" s="26" t="n">
-        <v>180.42</v>
-      </c>
-      <c r="D1065" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1065" s="28" t="n"/>
+      <c r="D1065" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1065" s="24" t="n"/>
     </row>
     <row r="1066" ht="22.5" customHeight="1">
       <c r="B1066" s="25" t="inlineStr">
         <is>
-          <t>Окислитель Welloxon Perfect 4% 1000мл ДЛЯ ПАСТЕЛЬНОГО ТОНИРОВАНИЯ 6496</t>
+          <t>Окислитель Welloxon Perfect 1,9% 1000мл ДЛЯ ПАСТЕЛЬНОГО ТОНИРОВАНИЯ 6495/6921</t>
         </is>
       </c>
       <c r="C1066" s="26" t="n">
@@ -17670,7 +17670,7 @@
     <row r="1067">
       <c r="B1067" s="25" t="inlineStr">
         <is>
-          <t>Окислитель Welloxon Perfect 6% 1000мл 6497/6923</t>
+          <t>Окислитель Welloxon Perfect 12% 1000мл 6499/6488</t>
         </is>
       </c>
       <c r="C1067" s="26" t="n">
@@ -17686,39 +17686,39 @@
     <row r="1068">
       <c r="B1068" s="25" t="inlineStr">
         <is>
-          <t>Окислитель Welloxon Perfect 9% 1000 мл. 6498/6484</t>
+          <t>Окислитель Welloxon Perfect 12% 60мл 6494/50931</t>
         </is>
       </c>
       <c r="C1068" s="26" t="n">
+        <v>180.42</v>
+      </c>
+      <c r="D1068" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1068" s="28" t="n"/>
+    </row>
+    <row r="1069" ht="22.5" customHeight="1">
+      <c r="B1069" s="25" t="inlineStr">
+        <is>
+          <t>Окислитель Welloxon Perfect 4% 1000мл ДЛЯ ПАСТЕЛЬНОГО ТОНИРОВАНИЯ 6496</t>
+        </is>
+      </c>
+      <c r="C1069" s="26" t="n">
         <v>928.6799999999999</v>
       </c>
-      <c r="D1068" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1068" s="28" t="n"/>
-    </row>
-    <row r="1069">
-      <c r="B1069" s="7" t="inlineStr">
-        <is>
-          <t>Оксид Color Touch 1,9 % 1000 мл. 6021/6298</t>
-        </is>
-      </c>
-      <c r="C1069" s="8" t="n">
-        <v>998.58</v>
-      </c>
-      <c r="D1069" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1069" s="24" t="n"/>
+      <c r="D1069" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1069" s="28" t="n"/>
     </row>
     <row r="1070">
       <c r="B1070" s="25" t="inlineStr">
         <is>
-          <t>Оксид Color Touch 4 % 1000 мл. 6019/6291</t>
+          <t>Окислитель Welloxon Perfect 6% 1000мл 6497/6923</t>
         </is>
       </c>
       <c r="C1070" s="26" t="n">
@@ -17734,11 +17734,11 @@
     <row r="1071">
       <c r="B1071" s="25" t="inlineStr">
         <is>
-          <t>Палитра Color Touch 21 12933</t>
+          <t>Окислитель Welloxon Perfect 9% 1000 мл. 6498/6484</t>
         </is>
       </c>
       <c r="C1071" s="26" t="n">
-        <v>425</v>
+        <v>928.6799999999999</v>
       </c>
       <c r="D1071" s="27" t="inlineStr">
         <is>
@@ -17747,40 +17747,46 @@
       </c>
       <c r="E1071" s="28" t="n"/>
     </row>
-    <row r="1072" ht="28.5" customHeight="1">
-      <c r="B1072" s="12" t="inlineStr">
-        <is>
-          <t>SHINEFINITY - Гель-крем краска, цветное глазирование</t>
-        </is>
-      </c>
-      <c r="C1072" s="17" t="n"/>
-      <c r="D1072" s="22" t="n"/>
-      <c r="E1072" s="22" t="n"/>
+    <row r="1072">
+      <c r="B1072" s="7" t="inlineStr">
+        <is>
+          <t>Оксид Color Touch 1,9 % 1000 мл. 6021/6298</t>
+        </is>
+      </c>
+      <c r="C1072" s="8" t="n">
+        <v>998.58</v>
+      </c>
+      <c r="D1072" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1072" s="24" t="n"/>
     </row>
     <row r="1073">
-      <c r="B1073" s="7" t="inlineStr">
-        <is>
-          <t>SHINEFINITY 04/0 Натуральный Espresso 60мл 4/0</t>
-        </is>
-      </c>
-      <c r="C1073" s="8" t="n">
-        <v>715</v>
-      </c>
-      <c r="D1073" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1073" s="24" t="n"/>
+      <c r="B1073" s="25" t="inlineStr">
+        <is>
+          <t>Оксид Color Touch 4 % 1000 мл. 6019/6291</t>
+        </is>
+      </c>
+      <c r="C1073" s="26" t="n">
+        <v>928.6799999999999</v>
+      </c>
+      <c r="D1073" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1073" s="28" t="n"/>
     </row>
     <row r="1074">
       <c r="B1074" s="25" t="inlineStr">
         <is>
-          <t>SHINEFINITY 04/07 Горький шоколад 60мл 4/07</t>
+          <t>Палитра Color Touch 21 12933</t>
         </is>
       </c>
       <c r="C1074" s="26" t="n">
-        <v>664.95</v>
+        <v>425</v>
       </c>
       <c r="D1074" s="27" t="inlineStr">
         <is>
@@ -17789,26 +17795,20 @@
       </c>
       <c r="E1074" s="28" t="n"/>
     </row>
-    <row r="1075">
-      <c r="B1075" s="7" t="inlineStr">
-        <is>
-          <t>SHINEFINITY 06/0 Натуральный Brandy 60мл 6/0</t>
-        </is>
-      </c>
-      <c r="C1075" s="8" t="n">
-        <v>715</v>
-      </c>
-      <c r="D1075" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1075" s="24" t="n"/>
+    <row r="1075" ht="28.5" customHeight="1">
+      <c r="B1075" s="12" t="inlineStr">
+        <is>
+          <t>SHINEFINITY - Гель-крем краска, цветное глазирование</t>
+        </is>
+      </c>
+      <c r="C1075" s="17" t="n"/>
+      <c r="D1075" s="22" t="n"/>
+      <c r="E1075" s="22" t="n"/>
     </row>
     <row r="1076">
       <c r="B1076" s="7" t="inlineStr">
         <is>
-          <t>SHINEFINITY 06/02 Темный шалфей 60мл 6/02</t>
+          <t>SHINEFINITY 04/0 Натуральный Espresso 60мл 4/0</t>
         </is>
       </c>
       <c r="C1076" s="8" t="n">
@@ -17822,41 +17822,41 @@
       <c r="E1076" s="24" t="n"/>
     </row>
     <row r="1077">
-      <c r="B1077" s="7" t="inlineStr">
-        <is>
-          <t>SHINEFINITY 06/07 Грецкий орех 60мл 6/07</t>
-        </is>
-      </c>
-      <c r="C1077" s="8" t="n">
+      <c r="B1077" s="25" t="inlineStr">
+        <is>
+          <t>SHINEFINITY 04/07 Горький шоколад 60мл 4/07</t>
+        </is>
+      </c>
+      <c r="C1077" s="26" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="D1077" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1077" s="28" t="n"/>
+    </row>
+    <row r="1078">
+      <c r="B1078" s="7" t="inlineStr">
+        <is>
+          <t>SHINEFINITY 06/0 Натуральный Brandy 60мл 6/0</t>
+        </is>
+      </c>
+      <c r="C1078" s="8" t="n">
         <v>715</v>
       </c>
-      <c r="D1077" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1077" s="24" t="n"/>
-    </row>
-    <row r="1078">
-      <c r="B1078" s="25" t="inlineStr">
-        <is>
-          <t>SHINEFINITY 06/71 Ледяной орех 60мл 6/71</t>
-        </is>
-      </c>
-      <c r="C1078" s="26" t="n">
-        <v>664.95</v>
-      </c>
-      <c r="D1078" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1078" s="28" t="n"/>
+      <c r="D1078" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1078" s="24" t="n"/>
     </row>
     <row r="1079">
       <c r="B1079" s="7" t="inlineStr">
         <is>
-          <t>SHINEFINITY 07/12 Матовый блонд 60мл 7/12</t>
+          <t>SHINEFINITY 06/02 Темный шалфей 60мл 6/02</t>
         </is>
       </c>
       <c r="C1079" s="8" t="n">
@@ -17872,7 +17872,7 @@
     <row r="1080">
       <c r="B1080" s="7" t="inlineStr">
         <is>
-          <t>SHINEFINITY 07/13 Тоффи-крем 60мл 7/13</t>
+          <t>SHINEFINITY 06/07 Грецкий орех 60мл 6/07</t>
         </is>
       </c>
       <c r="C1080" s="8" t="n">
@@ -17886,25 +17886,25 @@
       <c r="E1080" s="24" t="n"/>
     </row>
     <row r="1081">
-      <c r="B1081" s="7" t="inlineStr">
-        <is>
-          <t>SHINEFINITY 07/81 Дымчатый опал 60мл 7/81</t>
-        </is>
-      </c>
-      <c r="C1081" s="8" t="n">
-        <v>715</v>
-      </c>
-      <c r="D1081" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1081" s="24" t="n"/>
+      <c r="B1081" s="25" t="inlineStr">
+        <is>
+          <t>SHINEFINITY 06/71 Ледяной орех 60мл 6/71</t>
+        </is>
+      </c>
+      <c r="C1081" s="26" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="D1081" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1081" s="28" t="n"/>
     </row>
     <row r="1082">
       <c r="B1082" s="7" t="inlineStr">
         <is>
-          <t>SHINEFINITY 08/0 Натуральный Latte 60мл 8/0</t>
+          <t>SHINEFINITY 07/12 Матовый блонд 60мл 7/12</t>
         </is>
       </c>
       <c r="C1082" s="8" t="n">
@@ -17920,7 +17920,7 @@
     <row r="1083">
       <c r="B1083" s="7" t="inlineStr">
         <is>
-          <t>SHINEFINITY 08/38 Медовое латте 60мл 8/38</t>
+          <t>SHINEFINITY 07/13 Тоффи-крем 60мл 7/13</t>
         </is>
       </c>
       <c r="C1083" s="8" t="n">
@@ -17936,7 +17936,7 @@
     <row r="1084">
       <c r="B1084" s="7" t="inlineStr">
         <is>
-          <t>SHINEFINITY 08/98 Серебряный жемчуг 60мл 8/98</t>
+          <t>SHINEFINITY 07/81 Дымчатый опал 60мл 7/81</t>
         </is>
       </c>
       <c r="C1084" s="8" t="n">
@@ -17952,7 +17952,7 @@
     <row r="1085">
       <c r="B1085" s="7" t="inlineStr">
         <is>
-          <t>SHINEFINITY 09/02 Пустынный шалфей 60мл 9/02</t>
+          <t>SHINEFINITY 08/0 Натуральный Latte 60мл 8/0</t>
         </is>
       </c>
       <c r="C1085" s="8" t="n">
@@ -17966,25 +17966,25 @@
       <c r="E1085" s="24" t="n"/>
     </row>
     <row r="1086">
-      <c r="B1086" s="25" t="inlineStr">
-        <is>
-          <t>SHINEFINITY 09/36 Ванильная глазурь 60мл 9/36</t>
-        </is>
-      </c>
-      <c r="C1086" s="26" t="n">
-        <v>664.95</v>
-      </c>
-      <c r="D1086" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1086" s="28" t="n"/>
+      <c r="B1086" s="7" t="inlineStr">
+        <is>
+          <t>SHINEFINITY 08/38 Медовое латте 60мл 8/38</t>
+        </is>
+      </c>
+      <c r="C1086" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="D1086" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1086" s="24" t="n"/>
     </row>
     <row r="1087">
       <c r="B1087" s="7" t="inlineStr">
         <is>
-          <t>SHINEFINITY 09/65 Розовое сияние 60мл 9/65</t>
+          <t>SHINEFINITY 08/98 Серебряный жемчуг 60мл 8/98</t>
         </is>
       </c>
       <c r="C1087" s="8" t="n">
@@ -18000,7 +18000,7 @@
     <row r="1088">
       <c r="B1088" s="7" t="inlineStr">
         <is>
-          <t>SHINEFINITY 09/73 Карамельное молоко 60мл 9/73</t>
+          <t>SHINEFINITY 09/02 Пустынный шалфей 60мл 9/02</t>
         </is>
       </c>
       <c r="C1088" s="8" t="n">
@@ -18014,25 +18014,25 @@
       <c r="E1088" s="24" t="n"/>
     </row>
     <row r="1089">
-      <c r="B1089" s="7" t="inlineStr">
-        <is>
-          <t>SHINEFINITY 10/0 Светлый блондин натуральный 60мл 10/0</t>
-        </is>
-      </c>
-      <c r="C1089" s="8" t="n">
-        <v>715</v>
-      </c>
-      <c r="D1089" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1089" s="24" t="n"/>
+      <c r="B1089" s="25" t="inlineStr">
+        <is>
+          <t>SHINEFINITY 09/36 Ванильная глазурь 60мл 9/36</t>
+        </is>
+      </c>
+      <c r="C1089" s="26" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="D1089" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1089" s="28" t="n"/>
     </row>
     <row r="1090">
       <c r="B1090" s="7" t="inlineStr">
         <is>
-          <t>SHINEFINITY 10/6 Светлый блондин лавандовый 60мл 10/6</t>
+          <t>SHINEFINITY 09/65 Розовое сияние 60мл 9/65</t>
         </is>
       </c>
       <c r="C1090" s="8" t="n">
@@ -18048,47 +18048,59 @@
     <row r="1091">
       <c r="B1091" s="7" t="inlineStr">
         <is>
+          <t>SHINEFINITY 09/73 Карамельное молоко 60мл 9/73</t>
+        </is>
+      </c>
+      <c r="C1091" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="D1091" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1091" s="24" t="n"/>
+    </row>
+    <row r="1092">
+      <c r="B1092" s="7" t="inlineStr">
+        <is>
+          <t>SHINEFINITY 10/0 Светлый блондин натуральный 60мл 10/0</t>
+        </is>
+      </c>
+      <c r="C1092" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="D1092" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1092" s="24" t="n"/>
+    </row>
+    <row r="1093">
+      <c r="B1093" s="7" t="inlineStr">
+        <is>
+          <t>SHINEFINITY 10/6 Светлый блондин лавандовый 60мл 10/6</t>
+        </is>
+      </c>
+      <c r="C1093" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="D1093" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1093" s="24" t="n"/>
+    </row>
+    <row r="1094">
+      <c r="B1094" s="7" t="inlineStr">
+        <is>
           <t>SHINEFINITY Активатор для нанесения кисточкой 60мл</t>
         </is>
       </c>
-      <c r="C1091" s="8" t="n">
+      <c r="C1094" s="8" t="n">
         <v>235</v>
-      </c>
-      <c r="D1091" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1091" s="24" t="n"/>
-    </row>
-    <row r="1092" ht="15" customHeight="1">
-      <c r="B1092" s="5" t="inlineStr">
-        <is>
-          <t>Корея</t>
-        </is>
-      </c>
-      <c r="C1092" s="16" t="n"/>
-      <c r="D1092" s="22" t="n"/>
-      <c r="E1092" s="22" t="n"/>
-    </row>
-    <row r="1093" ht="14.25" customHeight="1">
-      <c r="B1093" s="12" t="inlineStr">
-        <is>
-          <t>La`Dor</t>
-        </is>
-      </c>
-      <c r="C1093" s="17" t="n"/>
-      <c r="D1093" s="22" t="n"/>
-      <c r="E1093" s="22" t="n"/>
-    </row>
-    <row r="1094" ht="22.5" customHeight="1">
-      <c r="B1094" s="7" t="inlineStr">
-        <is>
-          <t>Филлер для восстановления волос Perfect Hair Fill-Up 13 мл 845623/лд2</t>
-        </is>
-      </c>
-      <c r="C1094" s="8" t="n">
-        <v>120</v>
       </c>
       <c r="D1094" s="23" t="inlineStr">
         <is>
@@ -18100,37 +18112,31 @@
     <row r="1095" ht="15" customHeight="1">
       <c r="B1095" s="5" t="inlineStr">
         <is>
-          <t>ОДНОРАЗОВАЯ ПРОДУКЦИЯ</t>
+          <t>Корея</t>
         </is>
       </c>
       <c r="C1095" s="16" t="n"/>
       <c r="D1095" s="22" t="n"/>
       <c r="E1095" s="22" t="n"/>
     </row>
-    <row r="1096">
-      <c r="B1096" s="7" t="inlineStr">
-        <is>
-          <t>Бахилы ПЭ 100шт. 01-606</t>
-        </is>
-      </c>
-      <c r="C1096" s="8" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="D1096" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1096" s="24" t="n"/>
-    </row>
-    <row r="1097">
+    <row r="1096" ht="14.25" customHeight="1">
+      <c r="B1096" s="12" t="inlineStr">
+        <is>
+          <t>La`Dor</t>
+        </is>
+      </c>
+      <c r="C1096" s="17" t="n"/>
+      <c r="D1096" s="22" t="n"/>
+      <c r="E1096" s="22" t="n"/>
+    </row>
+    <row r="1097" ht="22.5" customHeight="1">
       <c r="B1097" s="7" t="inlineStr">
         <is>
-          <t>Воротнички бумажные 500шт 01-331</t>
+          <t>Филлер для восстановления волос Perfect Hair Fill-Up 13 мл 845623/лд2</t>
         </is>
       </c>
       <c r="C1097" s="8" t="n">
-        <v>387.23</v>
+        <v>120</v>
       </c>
       <c r="D1097" s="23" t="inlineStr">
         <is>
@@ -18139,30 +18145,24 @@
       </c>
       <c r="E1097" s="24" t="n"/>
     </row>
-    <row r="1098">
-      <c r="B1098" s="7" t="inlineStr">
-        <is>
-          <t>Воротнички мягкие 7х40 100шт 00-662</t>
-        </is>
-      </c>
-      <c r="C1098" s="8" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="D1098" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1098" s="24" t="n"/>
+    <row r="1098" ht="15" customHeight="1">
+      <c r="B1098" s="5" t="inlineStr">
+        <is>
+          <t>ОДНОРАЗОВАЯ ПРОДУКЦИЯ</t>
+        </is>
+      </c>
+      <c r="C1098" s="16" t="n"/>
+      <c r="D1098" s="22" t="n"/>
+      <c r="E1098" s="22" t="n"/>
     </row>
     <row r="1099">
       <c r="B1099" s="7" t="inlineStr">
         <is>
-          <t>Крафт-пакет с индикатором 100х250мм 03-142</t>
+          <t>Бахилы ПЭ 100шт. 01-606</t>
         </is>
       </c>
       <c r="C1099" s="8" t="n">
-        <v>354.09</v>
+        <v>101.6</v>
       </c>
       <c r="D1099" s="23" t="inlineStr">
         <is>
@@ -18174,11 +18174,11 @@
     <row r="1100">
       <c r="B1100" s="7" t="inlineStr">
         <is>
-          <t>Пелерина п/э 25шт 01-681/10-654</t>
+          <t>Воротнички бумажные 500шт 01-331</t>
         </is>
       </c>
       <c r="C1100" s="8" t="n">
-        <v>97.75</v>
+        <v>387.23</v>
       </c>
       <c r="D1100" s="23" t="inlineStr">
         <is>
@@ -18187,14 +18187,14 @@
       </c>
       <c r="E1100" s="24" t="n"/>
     </row>
-    <row r="1101" ht="22.5" customHeight="1">
+    <row r="1101">
       <c r="B1101" s="7" t="inlineStr">
         <is>
-          <t>Пеньюары одноразовые КОМФОРТ 100*160 см 50шт/уп (серебристый) 01-933</t>
+          <t>Воротнички мягкие 7х40 100шт 00-662</t>
         </is>
       </c>
       <c r="C1101" s="8" t="n">
-        <v>690</v>
+        <v>87.5</v>
       </c>
       <c r="D1101" s="23" t="inlineStr">
         <is>
@@ -18206,11 +18206,11 @@
     <row r="1102">
       <c r="B1102" s="7" t="inlineStr">
         <is>
-          <t>Пеньюары одноразовые СТАНДАРТ 100*140см 50шт/уп 01-882</t>
+          <t>Крафт-пакет с индикатором 100х250мм 03-142</t>
         </is>
       </c>
       <c r="C1102" s="8" t="n">
-        <v>387</v>
+        <v>354.09</v>
       </c>
       <c r="D1102" s="23" t="inlineStr">
         <is>
@@ -18222,11 +18222,11 @@
     <row r="1103">
       <c r="B1103" s="7" t="inlineStr">
         <is>
-          <t>Пеньюары одноразовые СТАНДАРТ 100*160 см 50шт/уп 01-879</t>
+          <t>Пелерина п/э 25шт 01-681/10-654</t>
         </is>
       </c>
       <c r="C1103" s="8" t="n">
-        <v>420</v>
+        <v>97.75</v>
       </c>
       <c r="D1103" s="23" t="inlineStr">
         <is>
@@ -18235,14 +18235,14 @@
       </c>
       <c r="E1103" s="24" t="n"/>
     </row>
-    <row r="1104">
+    <row r="1104" ht="22.5" customHeight="1">
       <c r="B1104" s="7" t="inlineStr">
         <is>
-          <t>Пеньюары одноразовые СТАНДАРТ 120*160см 50шт/уп 03-729</t>
+          <t>Пеньюары одноразовые КОМФОРТ 100*160 см 50шт/уп (серебристый) 01-933</t>
         </is>
       </c>
       <c r="C1104" s="8" t="n">
-        <v>525</v>
+        <v>690</v>
       </c>
       <c r="D1104" s="23" t="inlineStr">
         <is>
@@ -18254,11 +18254,11 @@
     <row r="1105">
       <c r="B1105" s="7" t="inlineStr">
         <is>
-          <t>перчатки виниловые,смотр.н/о "L" 100шт 01-943</t>
+          <t>Пеньюары одноразовые СТАНДАРТ 100*140см 50шт/уп 01-882</t>
         </is>
       </c>
       <c r="C1105" s="8" t="n">
-        <v>901.25</v>
+        <v>387</v>
       </c>
       <c r="D1105" s="23" t="inlineStr">
         <is>
@@ -18270,11 +18270,11 @@
     <row r="1106">
       <c r="B1106" s="7" t="inlineStr">
         <is>
-          <t>Перчатки нитриловые голубые "L" 200шт (100пар) 0200-233</t>
-        </is>
-      </c>
-      <c r="C1106" s="10" t="n">
-        <v>1625</v>
+          <t>Пеньюары одноразовые СТАНДАРТ 100*160 см 50шт/уп 01-879</t>
+        </is>
+      </c>
+      <c r="C1106" s="8" t="n">
+        <v>420</v>
       </c>
       <c r="D1106" s="23" t="inlineStr">
         <is>
@@ -18286,11 +18286,11 @@
     <row r="1107">
       <c r="B1107" s="7" t="inlineStr">
         <is>
-          <t>перчатки нитриловые голубые "M" 200 шт. (100 пар) 0200-234</t>
+          <t>Пеньюары одноразовые СТАНДАРТ 120*160см 50шт/уп 03-729</t>
         </is>
       </c>
       <c r="C1107" s="8" t="n">
-        <v>750</v>
+        <v>525</v>
       </c>
       <c r="D1107" s="23" t="inlineStr">
         <is>
@@ -18302,11 +18302,11 @@
     <row r="1108">
       <c r="B1108" s="7" t="inlineStr">
         <is>
-          <t>перчатки нитриловые розовые "XS" 03-183</t>
-        </is>
-      </c>
-      <c r="C1108" s="10" t="n">
-        <v>1105</v>
+          <t>перчатки виниловые,смотр.н/о "L" 100шт 01-943</t>
+        </is>
+      </c>
+      <c r="C1108" s="8" t="n">
+        <v>901.25</v>
       </c>
       <c r="D1108" s="23" t="inlineStr">
         <is>
@@ -18318,11 +18318,11 @@
     <row r="1109">
       <c r="B1109" s="7" t="inlineStr">
         <is>
-          <t>перчатки нитриловые фиолетовые "S" 100 пар (200 шт.) 0200-235</t>
+          <t>Перчатки нитриловые голубые "L" 200шт (100пар) 0200-233</t>
         </is>
       </c>
       <c r="C1109" s="10" t="n">
-        <v>1394.44</v>
+        <v>1625</v>
       </c>
       <c r="D1109" s="23" t="inlineStr">
         <is>
@@ -18334,11 +18334,11 @@
     <row r="1110">
       <c r="B1110" s="7" t="inlineStr">
         <is>
-          <t>Перчатки нитриловые черные "L" 100шт 11-675</t>
+          <t>перчатки нитриловые голубые "M" 200 шт. (100 пар) 0200-234</t>
         </is>
       </c>
       <c r="C1110" s="8" t="n">
-        <v>376.05</v>
+        <v>750</v>
       </c>
       <c r="D1110" s="23" t="inlineStr">
         <is>
@@ -18350,11 +18350,11 @@
     <row r="1111">
       <c r="B1111" s="7" t="inlineStr">
         <is>
-          <t>Перчатки нитриловые черные "M" 100шт 11-676/50549</t>
-        </is>
-      </c>
-      <c r="C1111" s="8" t="n">
-        <v>376</v>
+          <t>перчатки нитриловые розовые "XS" 03-183</t>
+        </is>
+      </c>
+      <c r="C1111" s="10" t="n">
+        <v>1105</v>
       </c>
       <c r="D1111" s="23" t="inlineStr">
         <is>
@@ -18366,11 +18366,11 @@
     <row r="1112">
       <c r="B1112" s="7" t="inlineStr">
         <is>
-          <t>перчатки нитриловые черные "S" 100 шт. 604-188</t>
-        </is>
-      </c>
-      <c r="C1112" s="8" t="n">
-        <v>376</v>
+          <t>перчатки нитриловые фиолетовые "S" 100 пар (200 шт.) 0200-235</t>
+        </is>
+      </c>
+      <c r="C1112" s="10" t="n">
+        <v>1394.44</v>
       </c>
       <c r="D1112" s="23" t="inlineStr">
         <is>
@@ -18382,11 +18382,11 @@
     <row r="1113">
       <c r="B1113" s="7" t="inlineStr">
         <is>
-          <t>Перчатки нитриловые черные "XS" 100шт 11-462</t>
+          <t>Перчатки нитриловые черные "L" 100шт 11-675</t>
         </is>
       </c>
       <c r="C1113" s="8" t="n">
-        <v>376</v>
+        <v>376.05</v>
       </c>
       <c r="D1113" s="23" t="inlineStr">
         <is>
@@ -18398,11 +18398,11 @@
     <row r="1114">
       <c r="B1114" s="7" t="inlineStr">
         <is>
-          <t>Полотенце COTTO 35x70 см. №50 шт. 601-066</t>
+          <t>Перчатки нитриловые черные "M" 100шт 11-676/50549</t>
         </is>
       </c>
       <c r="C1114" s="8" t="n">
-        <v>489.55</v>
+        <v>376</v>
       </c>
       <c r="D1114" s="23" t="inlineStr">
         <is>
@@ -18414,11 +18414,11 @@
     <row r="1115">
       <c r="B1115" s="7" t="inlineStr">
         <is>
-          <t>Полотенце Стандарт 35x70 см. №100 шт. 01-359/SL-S35-100</t>
+          <t>перчатки нитриловые черные "S" 100 шт. 604-188</t>
         </is>
       </c>
       <c r="C1115" s="8" t="n">
-        <v>701.99</v>
+        <v>376</v>
       </c>
       <c r="D1115" s="23" t="inlineStr">
         <is>
@@ -18430,139 +18430,139 @@
     <row r="1116">
       <c r="B1116" s="7" t="inlineStr">
         <is>
+          <t>Перчатки нитриловые черные "XS" 100шт 11-462</t>
+        </is>
+      </c>
+      <c r="C1116" s="8" t="n">
+        <v>376</v>
+      </c>
+      <c r="D1116" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1116" s="24" t="n"/>
+    </row>
+    <row r="1117">
+      <c r="B1117" s="7" t="inlineStr">
+        <is>
+          <t>Полотенце COTTO 35x70 см. №50 шт. 601-066</t>
+        </is>
+      </c>
+      <c r="C1117" s="8" t="n">
+        <v>489.55</v>
+      </c>
+      <c r="D1117" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1117" s="24" t="n"/>
+    </row>
+    <row r="1118">
+      <c r="B1118" s="7" t="inlineStr">
+        <is>
+          <t>Полотенце Стандарт 35x70 см. №100 шт. 01-359/SL-S35-100</t>
+        </is>
+      </c>
+      <c r="C1118" s="8" t="n">
+        <v>701.99</v>
+      </c>
+      <c r="D1118" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1118" s="24" t="n"/>
+    </row>
+    <row r="1119">
+      <c r="B1119" s="7" t="inlineStr">
+        <is>
           <t>Полотенце Стандарт 45x90 см. №50 шт. 01-349/EL-S45-50</t>
         </is>
       </c>
-      <c r="C1116" s="8" t="n">
+      <c r="C1119" s="8" t="n">
         <v>599</v>
       </c>
-      <c r="D1116" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1116" s="24" t="n"/>
-    </row>
-    <row r="1117" ht="22.5" customHeight="1">
-      <c r="B1117" s="7" t="inlineStr">
+      <c r="D1119" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1119" s="24" t="n"/>
+    </row>
+    <row r="1120" ht="22.5" customHeight="1">
+      <c r="B1120" s="7" t="inlineStr">
         <is>
           <t>Полотонца Ван тач Soft Хлопок\сетка ЛЮКС белый 35*70  100шт\уп пластом 07-657-100</t>
         </is>
       </c>
-      <c r="C1117" s="8" t="n">
+      <c r="C1120" s="8" t="n">
         <v>865</v>
       </c>
-      <c r="D1117" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1117" s="24" t="n"/>
-    </row>
-    <row r="1118" ht="22.5" customHeight="1">
-      <c r="B1118" s="7" t="inlineStr">
+      <c r="D1120" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1120" s="24" t="n"/>
+    </row>
+    <row r="1121" ht="22.5" customHeight="1">
+      <c r="B1121" s="7" t="inlineStr">
         <is>
           <t>Полотонца Ван тач Soft Хлопок\сетка ЛЮКС белый 35*70 50шт\уп пластом 07-656-50</t>
         </is>
       </c>
-      <c r="C1118" s="8" t="n">
+      <c r="C1121" s="8" t="n">
         <v>435</v>
       </c>
-      <c r="D1118" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1118" s="24" t="n"/>
-    </row>
-    <row r="1119" ht="22.5" customHeight="1">
-      <c r="B1119" s="7" t="inlineStr">
+      <c r="D1121" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1121" s="24" t="n"/>
+    </row>
+    <row r="1122" ht="22.5" customHeight="1">
+      <c r="B1122" s="7" t="inlineStr">
         <is>
           <t>Полотонца Ван тач Soft Хлопок\сетка ЛЮКС белый 45*90 50шт\уп пластом 07-662-50</t>
         </is>
       </c>
-      <c r="C1119" s="8" t="n">
+      <c r="C1122" s="8" t="n">
         <v>725</v>
       </c>
-      <c r="D1119" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1119" s="24" t="n"/>
-    </row>
-    <row r="1120">
-      <c r="B1120" s="25" t="inlineStr">
+      <c r="D1122" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1122" s="24" t="n"/>
+    </row>
+    <row r="1123">
+      <c r="B1123" s="25" t="inlineStr">
         <is>
           <t>Салфетки 20х20 200 шт. в рулоне 00-144-200</t>
         </is>
       </c>
-      <c r="C1120" s="26" t="n">
+      <c r="C1123" s="26" t="n">
         <v>237.15</v>
       </c>
-      <c r="D1120" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1120" s="28" t="n"/>
-    </row>
-    <row r="1121">
-      <c r="B1121" s="7" t="inlineStr">
-        <is>
-          <t>Салфетки 30х40 100шт. 00-147</t>
-        </is>
-      </c>
-      <c r="C1121" s="8" t="n">
-        <v>358.75</v>
-      </c>
-      <c r="D1121" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1121" s="24" t="n"/>
-    </row>
-    <row r="1122">
-      <c r="B1122" s="7" t="inlineStr">
-        <is>
-          <t>Фартук п/э 70х120 50шт. 01-626</t>
-        </is>
-      </c>
-      <c r="C1122" s="8" t="n">
-        <v>247.04</v>
-      </c>
-      <c r="D1122" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1122" s="24" t="n"/>
-    </row>
-    <row r="1123">
-      <c r="B1123" s="7" t="inlineStr">
-        <is>
-          <t>фольга 12см*100м*16мкр тисненая 006996</t>
-        </is>
-      </c>
-      <c r="C1123" s="8" t="n">
-        <v>470</v>
-      </c>
-      <c r="D1123" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1123" s="24" t="n"/>
+      <c r="D1123" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1123" s="28" t="n"/>
     </row>
     <row r="1124">
       <c r="B1124" s="7" t="inlineStr">
         <is>
-          <t>фольга 12см*100м*18мкр 001838</t>
+          <t>Салфетки 30х40 100шт. 00-147</t>
         </is>
       </c>
       <c r="C1124" s="8" t="n">
-        <v>390</v>
+        <v>358.75</v>
       </c>
       <c r="D1124" s="23" t="inlineStr">
         <is>
@@ -18574,11 +18574,11 @@
     <row r="1125">
       <c r="B1125" s="7" t="inlineStr">
         <is>
-          <t>фольга 12см*100м*18мкр тисненая 006997</t>
+          <t>Фартук п/э 70х120 50шт. 01-626</t>
         </is>
       </c>
       <c r="C1125" s="8" t="n">
-        <v>490</v>
+        <v>247.04</v>
       </c>
       <c r="D1125" s="23" t="inlineStr">
         <is>
@@ -18590,11 +18590,11 @@
     <row r="1126">
       <c r="B1126" s="7" t="inlineStr">
         <is>
-          <t>фольга 12см*25м*16мкр фа25</t>
+          <t>фольга 12см*100м*16мкр тисненая 006996</t>
         </is>
       </c>
       <c r="C1126" s="8" t="n">
-        <v>86.34</v>
+        <v>470</v>
       </c>
       <c r="D1126" s="23" t="inlineStr">
         <is>
@@ -18606,11 +18606,11 @@
     <row r="1127">
       <c r="B1127" s="7" t="inlineStr">
         <is>
-          <t>фольга 12см*25м*18мкр 03-449/ф25</t>
+          <t>фольга 12см*100м*18мкр 001838</t>
         </is>
       </c>
       <c r="C1127" s="8" t="n">
-        <v>95</v>
+        <v>390</v>
       </c>
       <c r="D1127" s="23" t="inlineStr">
         <is>
@@ -18622,11 +18622,11 @@
     <row r="1128">
       <c r="B1128" s="7" t="inlineStr">
         <is>
-          <t>фольга 12см*50м*18мкр 03-450/ф50</t>
+          <t>фольга 12см*100м*18мкр тисненая 006997</t>
         </is>
       </c>
       <c r="C1128" s="8" t="n">
-        <v>203.44</v>
+        <v>490</v>
       </c>
       <c r="D1128" s="23" t="inlineStr">
         <is>
@@ -18638,45 +18638,90 @@
     <row r="1129">
       <c r="B1129" s="7" t="inlineStr">
         <is>
+          <t>фольга 12см*25м*16мкр фа25</t>
+        </is>
+      </c>
+      <c r="C1129" s="8" t="n">
+        <v>86.34</v>
+      </c>
+      <c r="D1129" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1129" s="24" t="n"/>
+    </row>
+    <row r="1130">
+      <c r="B1130" s="7" t="inlineStr">
+        <is>
+          <t>фольга 12см*25м*18мкр 03-449/ф25</t>
+        </is>
+      </c>
+      <c r="C1130" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="D1130" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1130" s="24" t="n"/>
+    </row>
+    <row r="1131">
+      <c r="B1131" s="7" t="inlineStr">
+        <is>
+          <t>фольга 12см*50м*18мкр 03-450/ф50</t>
+        </is>
+      </c>
+      <c r="C1131" s="8" t="n">
+        <v>203.44</v>
+      </c>
+      <c r="D1131" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1131" s="24" t="n"/>
+    </row>
+    <row r="1132">
+      <c r="B1132" s="7" t="inlineStr">
+        <is>
           <t>Шапочки "Шарлотка" 50 шт ,ЧЕРНЫЕ 603-208</t>
         </is>
       </c>
-      <c r="C1129" s="8" t="n">
+      <c r="C1132" s="8" t="n">
         <v>110.94</v>
       </c>
-      <c r="D1129" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1129" s="24" t="n"/>
-    </row>
-    <row r="1130">
-      <c r="B1130" s="30" t="inlineStr">
+      <c r="D1132" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1132" s="24" t="n"/>
+    </row>
+    <row r="1133">
+      <c r="B1133" s="30" t="inlineStr">
         <is>
           <t>Шапочки "Шарлотка" 50 шт БЕЛЫЕ 601-729</t>
         </is>
       </c>
-      <c r="C1130" s="31" t="n">
+      <c r="C1133" s="31" t="n">
         <v>99</v>
       </c>
-      <c r="D1130" s="32" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E1130" s="33" t="n"/>
-    </row>
-    <row r="1131"/>
-    <row r="1132"/>
-    <row r="1133"/>
+      <c r="D1133" s="32" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E1133" s="33" t="n"/>
+    </row>
     <row r="1134"/>
-    <row r="1135" ht="22.5" customHeight="1"/>
-    <row r="1136" ht="22.5" customHeight="1"/>
-    <row r="1137" ht="22.5" customHeight="1"/>
-    <row r="1138"/>
-    <row r="1139"/>
-    <row r="1140"/>
+    <row r="1135"/>
+    <row r="1136"/>
+    <row r="1137"/>
+    <row r="1138" ht="22.5" customHeight="1"/>
+    <row r="1139" ht="22.5" customHeight="1"/>
+    <row r="1140" ht="22.5" customHeight="1"/>
     <row r="1141"/>
     <row r="1142"/>
     <row r="1143"/>
@@ -18685,35 +18730,38 @@
     <row r="1146"/>
     <row r="1147"/>
     <row r="1148"/>
-    <row r="1150" ht="15" customHeight="1"/>
+    <row r="1149"/>
+    <row r="1150"/>
+    <row r="1151"/>
+    <row r="1153" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C904:E904"/>
     <mergeCell ref="C531:E531"/>
-    <mergeCell ref="C856:E856"/>
-    <mergeCell ref="C1092:E1092"/>
-    <mergeCell ref="C919:E919"/>
+    <mergeCell ref="C1075:E1075"/>
+    <mergeCell ref="C1096:E1096"/>
     <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C850:E850"/>
-    <mergeCell ref="C865:E865"/>
+    <mergeCell ref="C853:E853"/>
     <mergeCell ref="C359:E359"/>
     <mergeCell ref="C39:E39"/>
     <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C868:E868"/>
     <mergeCell ref="C358:E358"/>
-    <mergeCell ref="C855:E855"/>
-    <mergeCell ref="C1072:E1072"/>
     <mergeCell ref="C749:E749"/>
-    <mergeCell ref="C1093:E1093"/>
+    <mergeCell ref="C858:E858"/>
+    <mergeCell ref="C847:E847"/>
+    <mergeCell ref="C907:E907"/>
+    <mergeCell ref="C1098:E1098"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="C748:E748"/>
+    <mergeCell ref="C922:E922"/>
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="C89:E89"/>
     <mergeCell ref="C1095:E1095"/>
-    <mergeCell ref="C844:E844"/>
     <mergeCell ref="C187:E187"/>
     <mergeCell ref="C184:E184"/>
+    <mergeCell ref="C859:E859"/>
     <mergeCell ref="C374:E374"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/prices/price-current.xlsx
+++ b/public/prices/price-current.xlsx
@@ -93,7 +93,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -355,13 +355,22 @@
       </top>
       <bottom style="medium"/>
     </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -463,6 +472,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -840,7 +853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1133"/>
+  <dimension ref="B1:F1133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="11.25"/>
   <cols>
     <col width="2.6640625" customWidth="1" min="1" max="1"/>
@@ -848,7 +861,7 @@
     <col width="15.33203125" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="256"/>
+    <col hidden="1" width="12" customWidth="1" min="6" max="256"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.25" customHeight="1">
@@ -906,10 +919,10 @@
           <t>CAREPROST</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n"/>
+      <c r="C6" s="45" t="n"/>
       <c r="D6" s="24" t="n"/>
-      <c r="E6" s="25" t="n"/>
-      <c r="F6" s="26" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="46" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="7" t="inlineStr">
@@ -936,10 +949,10 @@
           <t>CONCEPT</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
+      <c r="C8" s="47" t="n"/>
       <c r="D8" s="24" t="n"/>
-      <c r="E8" s="25" t="n"/>
-      <c r="F8" s="26" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="46" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="7" t="inlineStr">
@@ -1401,10 +1414,10 @@
           <t>DIKSON</t>
         </is>
       </c>
-      <c r="C33" s="16" t="n"/>
+      <c r="C33" s="45" t="n"/>
       <c r="D33" s="24" t="n"/>
-      <c r="E33" s="25" t="n"/>
-      <c r="F33" s="26" t="n"/>
+      <c r="E33" s="24" t="n"/>
+      <c r="F33" s="46" t="n"/>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="B34" s="7" t="inlineStr">
@@ -1450,10 +1463,10 @@
           <t>ESTEL</t>
         </is>
       </c>
-      <c r="C36" s="16" t="n"/>
+      <c r="C36" s="45" t="n"/>
       <c r="D36" s="24" t="n"/>
-      <c r="E36" s="25" t="n"/>
-      <c r="F36" s="26" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="46" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="7" t="inlineStr">
@@ -1499,10 +1512,10 @@
           <t>ISKARTES PROFESSIONAL</t>
         </is>
       </c>
-      <c r="C39" s="16" t="n"/>
+      <c r="C39" s="45" t="n"/>
       <c r="D39" s="24" t="n"/>
-      <c r="E39" s="25" t="n"/>
-      <c r="F39" s="26" t="n"/>
+      <c r="E39" s="24" t="n"/>
+      <c r="F39" s="46" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="33" t="inlineStr">
@@ -1586,10 +1599,10 @@
           <t>KAPOUS</t>
         </is>
       </c>
-      <c r="C44" s="31" t="n"/>
+      <c r="C44" s="47" t="n"/>
       <c r="D44" s="24" t="n"/>
-      <c r="E44" s="25" t="n"/>
-      <c r="F44" s="26" t="n"/>
+      <c r="E44" s="24" t="n"/>
+      <c r="F44" s="46" t="n"/>
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="B45" s="7" t="inlineStr">
@@ -2254,10 +2267,10 @@
           <t>L'OREAL</t>
         </is>
       </c>
-      <c r="C80" s="16" t="n"/>
+      <c r="C80" s="45" t="n"/>
       <c r="D80" s="24" t="n"/>
-      <c r="E80" s="25" t="n"/>
-      <c r="F80" s="26" t="n"/>
+      <c r="E80" s="24" t="n"/>
+      <c r="F80" s="46" t="n"/>
     </row>
     <row r="81">
       <c r="B81" s="7" t="inlineStr">
@@ -2417,10 +2430,10 @@
           <t>LEBEL</t>
         </is>
       </c>
-      <c r="C89" s="16" t="n"/>
+      <c r="C89" s="45" t="n"/>
       <c r="D89" s="24" t="n"/>
-      <c r="E89" s="25" t="n"/>
-      <c r="F89" s="26" t="n"/>
+      <c r="E89" s="24" t="n"/>
+      <c r="F89" s="46" t="n"/>
     </row>
     <row r="90">
       <c r="B90" s="7" t="inlineStr">
@@ -4214,10 +4227,10 @@
           <t>LEVISSIME</t>
         </is>
       </c>
-      <c r="C184" s="16" t="n"/>
+      <c r="C184" s="45" t="n"/>
       <c r="D184" s="24" t="n"/>
-      <c r="E184" s="25" t="n"/>
-      <c r="F184" s="26" t="n"/>
+      <c r="E184" s="24" t="n"/>
+      <c r="F184" s="46" t="n"/>
     </row>
     <row r="185">
       <c r="B185" s="7" t="inlineStr">
@@ -4263,10 +4276,10 @@
           <t>LONDA</t>
         </is>
       </c>
-      <c r="C187" s="16" t="n"/>
+      <c r="C187" s="45" t="n"/>
       <c r="D187" s="24" t="n"/>
-      <c r="E187" s="25" t="n"/>
-      <c r="F187" s="26" t="n"/>
+      <c r="E187" s="24" t="n"/>
+      <c r="F187" s="46" t="n"/>
     </row>
     <row r="188">
       <c r="B188" s="33" t="inlineStr">
@@ -7504,10 +7517,10 @@
           <t>MATRIX</t>
         </is>
       </c>
-      <c r="C358" s="16" t="n"/>
+      <c r="C358" s="45" t="n"/>
       <c r="D358" s="24" t="n"/>
-      <c r="E358" s="25" t="n"/>
-      <c r="F358" s="26" t="n"/>
+      <c r="E358" s="24" t="n"/>
+      <c r="F358" s="46" t="n"/>
     </row>
     <row r="359" ht="14.25" customHeight="1">
       <c r="B359" s="12" t="inlineStr">
@@ -7515,10 +7528,10 @@
           <t>Total Results New</t>
         </is>
       </c>
-      <c r="C359" s="17" t="n"/>
+      <c r="C359" s="48" t="n"/>
       <c r="D359" s="24" t="n"/>
-      <c r="E359" s="25" t="n"/>
-      <c r="F359" s="39" t="n"/>
+      <c r="E359" s="24" t="n"/>
+      <c r="F359" s="46" t="n"/>
     </row>
     <row r="360">
       <c r="B360" s="33" t="inlineStr">
@@ -7792,10 +7805,10 @@
           <t>MATRIX</t>
         </is>
       </c>
-      <c r="C374" s="17" t="n"/>
+      <c r="C374" s="48" t="n"/>
       <c r="D374" s="24" t="n"/>
-      <c r="E374" s="25" t="n"/>
-      <c r="F374" s="39" t="n"/>
+      <c r="E374" s="24" t="n"/>
+      <c r="F374" s="46" t="n"/>
     </row>
     <row r="375">
       <c r="B375" s="7" t="inlineStr">
@@ -10767,10 +10780,10 @@
           <t>OLLIN</t>
         </is>
       </c>
-      <c r="C531" s="16" t="n"/>
+      <c r="C531" s="45" t="n"/>
       <c r="D531" s="24" t="n"/>
-      <c r="E531" s="25" t="n"/>
-      <c r="F531" s="26" t="n"/>
+      <c r="E531" s="24" t="n"/>
+      <c r="F531" s="46" t="n"/>
     </row>
     <row r="532">
       <c r="B532" s="7" t="inlineStr">
@@ -14882,10 +14895,10 @@
           <t>SCHWARZKOPF</t>
         </is>
       </c>
-      <c r="C748" s="16" t="n"/>
+      <c r="C748" s="45" t="n"/>
       <c r="D748" s="24" t="n"/>
-      <c r="E748" s="25" t="n"/>
-      <c r="F748" s="26" t="n"/>
+      <c r="E748" s="24" t="n"/>
+      <c r="F748" s="46" t="n"/>
     </row>
     <row r="749" ht="28.5" customHeight="1">
       <c r="B749" s="12" t="inlineStr">
@@ -14893,10 +14906,10 @@
           <t>IGORA/BLONDME - Красители и специальные продукты</t>
         </is>
       </c>
-      <c r="C749" s="17" t="n"/>
+      <c r="C749" s="48" t="n"/>
       <c r="D749" s="24" t="n"/>
-      <c r="E749" s="25" t="n"/>
-      <c r="F749" s="39" t="n"/>
+      <c r="E749" s="24" t="n"/>
+      <c r="F749" s="46" t="n"/>
     </row>
     <row r="750">
       <c r="B750" s="33" t="inlineStr">
@@ -16747,10 +16760,10 @@
           <t>OSIS - Укладка</t>
         </is>
       </c>
-      <c r="C847" s="17" t="n"/>
+      <c r="C847" s="48" t="n"/>
       <c r="D847" s="24" t="n"/>
-      <c r="E847" s="25" t="n"/>
-      <c r="F847" s="39" t="n"/>
+      <c r="E847" s="24" t="n"/>
+      <c r="F847" s="46" t="n"/>
     </row>
     <row r="848">
       <c r="B848" s="33" t="inlineStr">
@@ -16853,10 +16866,10 @@
           <t>SILHOUETTE/Professionnelle - Укладка</t>
         </is>
       </c>
-      <c r="C853" s="17" t="n"/>
+      <c r="C853" s="48" t="n"/>
       <c r="D853" s="24" t="n"/>
-      <c r="E853" s="25" t="n"/>
-      <c r="F853" s="39" t="n"/>
+      <c r="E853" s="24" t="n"/>
+      <c r="F853" s="46" t="n"/>
     </row>
     <row r="854">
       <c r="B854" s="7" t="inlineStr">
@@ -16940,10 +16953,10 @@
           <t>WELLA</t>
         </is>
       </c>
-      <c r="C858" s="16" t="n"/>
+      <c r="C858" s="45" t="n"/>
       <c r="D858" s="24" t="n"/>
-      <c r="E858" s="25" t="n"/>
-      <c r="F858" s="26" t="n"/>
+      <c r="E858" s="24" t="n"/>
+      <c r="F858" s="46" t="n"/>
     </row>
     <row r="859" ht="14.25" customHeight="1">
       <c r="B859" s="12" t="inlineStr">
@@ -16951,10 +16964,10 @@
           <t>EIMI - Укладка</t>
         </is>
       </c>
-      <c r="C859" s="17" t="n"/>
+      <c r="C859" s="48" t="n"/>
       <c r="D859" s="24" t="n"/>
-      <c r="E859" s="25" t="n"/>
-      <c r="F859" s="39" t="n"/>
+      <c r="E859" s="24" t="n"/>
+      <c r="F859" s="46" t="n"/>
     </row>
     <row r="860">
       <c r="B860" s="33" t="inlineStr">
@@ -17114,10 +17127,10 @@
           <t>Illumina - Красители</t>
         </is>
       </c>
-      <c r="C868" s="17" t="n"/>
+      <c r="C868" s="48" t="n"/>
       <c r="D868" s="24" t="n"/>
-      <c r="E868" s="25" t="n"/>
-      <c r="F868" s="39" t="n"/>
+      <c r="E868" s="24" t="n"/>
+      <c r="F868" s="46" t="n"/>
     </row>
     <row r="869">
       <c r="B869" s="7" t="inlineStr">
@@ -17847,10 +17860,10 @@
           <t>INVIGO - Уход</t>
         </is>
       </c>
-      <c r="C907" s="17" t="n"/>
+      <c r="C907" s="48" t="n"/>
       <c r="D907" s="24" t="n"/>
-      <c r="E907" s="25" t="n"/>
-      <c r="F907" s="39" t="n"/>
+      <c r="E907" s="24" t="n"/>
+      <c r="F907" s="46" t="n"/>
     </row>
     <row r="908" ht="22.5" customHeight="1">
       <c r="B908" s="7" t="inlineStr">
@@ -18124,10 +18137,10 @@
           <t>KP Me+/CT - Красители и специальные продукты</t>
         </is>
       </c>
-      <c r="C922" s="17" t="n"/>
+      <c r="C922" s="48" t="n"/>
       <c r="D922" s="24" t="n"/>
-      <c r="E922" s="25" t="n"/>
-      <c r="F922" s="39" t="n"/>
+      <c r="E922" s="24" t="n"/>
+      <c r="F922" s="46" t="n"/>
     </row>
     <row r="923">
       <c r="B923" s="33" t="inlineStr">
@@ -21023,10 +21036,10 @@
           <t>SHINEFINITY - Гель-крем краска, цветное глазирование</t>
         </is>
       </c>
-      <c r="C1075" s="17" t="n"/>
+      <c r="C1075" s="48" t="n"/>
       <c r="D1075" s="24" t="n"/>
-      <c r="E1075" s="25" t="n"/>
-      <c r="F1075" s="39" t="n"/>
+      <c r="E1075" s="24" t="n"/>
+      <c r="F1075" s="46" t="n"/>
     </row>
     <row r="1076">
       <c r="B1076" s="7" t="inlineStr">
@@ -21395,10 +21408,10 @@
           <t>Корея</t>
         </is>
       </c>
-      <c r="C1095" s="16" t="n"/>
+      <c r="C1095" s="45" t="n"/>
       <c r="D1095" s="24" t="n"/>
-      <c r="E1095" s="25" t="n"/>
-      <c r="F1095" s="26" t="n"/>
+      <c r="E1095" s="24" t="n"/>
+      <c r="F1095" s="46" t="n"/>
     </row>
     <row r="1096" ht="14.25" customHeight="1">
       <c r="B1096" s="12" t="inlineStr">
@@ -21406,10 +21419,10 @@
           <t>La`Dor</t>
         </is>
       </c>
-      <c r="C1096" s="17" t="n"/>
+      <c r="C1096" s="48" t="n"/>
       <c r="D1096" s="24" t="n"/>
-      <c r="E1096" s="25" t="n"/>
-      <c r="F1096" s="39" t="n"/>
+      <c r="E1096" s="24" t="n"/>
+      <c r="F1096" s="46" t="n"/>
     </row>
     <row r="1097" ht="22.5" customHeight="1">
       <c r="B1097" s="7" t="inlineStr">
@@ -21436,10 +21449,10 @@
           <t>ОДНОРАЗОВАЯ ПРОДУКЦИЯ</t>
         </is>
       </c>
-      <c r="C1098" s="16" t="n"/>
+      <c r="C1098" s="45" t="n"/>
       <c r="D1098" s="24" t="n"/>
-      <c r="E1098" s="25" t="n"/>
-      <c r="F1098" s="26" t="n"/>
+      <c r="E1098" s="24" t="n"/>
+      <c r="F1098" s="46" t="n"/>
     </row>
     <row r="1099">
       <c r="B1099" s="7" t="inlineStr">
@@ -22106,24 +22119,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1134"/>
-    <row r="1135"/>
-    <row r="1136"/>
-    <row r="1137"/>
     <row r="1138" ht="22.5" customHeight="1"/>
     <row r="1139" ht="22.5" customHeight="1"/>
     <row r="1140" ht="22.5" customHeight="1"/>
-    <row r="1141"/>
-    <row r="1142"/>
-    <row r="1143"/>
-    <row r="1144"/>
-    <row r="1145"/>
-    <row r="1146"/>
-    <row r="1147"/>
-    <row r="1148"/>
-    <row r="1149"/>
-    <row r="1150"/>
-    <row r="1151"/>
     <row r="1153" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">

--- a/public/prices/price-current.xlsx
+++ b/public/prices/price-current.xlsx
@@ -2363,12 +2363,12 @@
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
-      <c r="B86" s="30" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>LEBEL</t>
         </is>
       </c>
-      <c r="C86" s="31" t="n"/>
+      <c r="C86" s="16" t="n"/>
       <c r="D86" s="24" t="n"/>
       <c r="E86" s="25" t="n"/>
       <c r="F86" s="26" t="n"/>
@@ -2388,7 +2388,9 @@
         </is>
       </c>
       <c r="E87" s="28" t="n"/>
-      <c r="F87" s="32" t="n"/>
+      <c r="F87" s="29" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="88">
       <c r="B88" s="7" t="inlineStr">
@@ -2424,7 +2426,9 @@
         </is>
       </c>
       <c r="E89" s="28" t="n"/>
-      <c r="F89" s="32" t="n"/>
+      <c r="F89" s="29" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="90">
       <c r="B90" s="7" t="inlineStr">
@@ -2460,7 +2464,9 @@
         </is>
       </c>
       <c r="E91" s="28" t="n"/>
-      <c r="F91" s="32" t="n"/>
+      <c r="F91" s="29" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="92">
       <c r="B92" s="7" t="inlineStr">
@@ -2496,7 +2502,9 @@
         </is>
       </c>
       <c r="E93" s="28" t="n"/>
-      <c r="F93" s="32" t="n"/>
+      <c r="F93" s="29" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="B94" s="7" t="inlineStr">
@@ -3615,7 +3623,9 @@
         </is>
       </c>
       <c r="E152" s="28" t="n"/>
-      <c r="F152" s="32" t="n"/>
+      <c r="F152" s="29" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="153" ht="22.5" customHeight="1">
       <c r="B153" s="7" t="inlineStr">
